--- a/compare/output/dscale_CO2_downscaled_SSP245.xlsx
+++ b/compare/output/dscale_CO2_downscaled_SSP245.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.140202</v>
+        <v>0.140201</v>
       </c>
       <c r="F2" t="n">
-        <v>0.203876</v>
+        <v>0.203874</v>
       </c>
       <c r="G2" t="n">
-        <v>0.247677</v>
+        <v>0.247674</v>
       </c>
       <c r="H2" t="n">
-        <v>0.295478</v>
+        <v>0.295471</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3495</v>
+        <v>0.349483</v>
       </c>
       <c r="J2" t="n">
         <v>1.487735</v>
@@ -684,13 +684,13 @@
         <v>0.302767</v>
       </c>
       <c r="G4" t="n">
-        <v>0.29717</v>
+        <v>0.297171</v>
       </c>
       <c r="H4" t="n">
-        <v>0.310198</v>
+        <v>0.3102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.341432</v>
+        <v>0.341435</v>
       </c>
       <c r="J4" t="n">
         <v>0.162231</v>
@@ -760,13 +760,13 @@
         <v>0.318408</v>
       </c>
       <c r="G5" t="n">
-        <v>0.489612</v>
+        <v>0.489611</v>
       </c>
       <c r="H5" t="n">
-        <v>0.709664</v>
+        <v>0.709662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9616980000000001</v>
+        <v>0.961693</v>
       </c>
       <c r="J5" t="n">
         <v>1.311947</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.386277</v>
+        <v>4.386275</v>
       </c>
       <c r="F6" t="n">
-        <v>6.288649</v>
+        <v>6.288641</v>
       </c>
       <c r="G6" t="n">
-        <v>6.942589</v>
+        <v>6.942571</v>
       </c>
       <c r="H6" t="n">
-        <v>7.714531</v>
+        <v>7.714491</v>
       </c>
       <c r="I6" t="n">
-        <v>8.875177000000001</v>
+        <v>8.875064</v>
       </c>
       <c r="J6" t="n">
         <v>16.138978</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.759568</v>
+        <v>5.75957</v>
       </c>
       <c r="F7" t="n">
-        <v>8.731208000000001</v>
+        <v>8.731216999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>11.488448</v>
+        <v>11.488469</v>
       </c>
       <c r="H7" t="n">
-        <v>15.034634</v>
+        <v>15.034686</v>
       </c>
       <c r="I7" t="n">
-        <v>19.586779</v>
+        <v>19.586937</v>
       </c>
       <c r="J7" t="n">
         <v>9.935786</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.109712</v>
+        <v>1.109711</v>
       </c>
       <c r="F8" t="n">
-        <v>1.585734</v>
+        <v>1.585732</v>
       </c>
       <c r="G8" t="n">
-        <v>1.925149</v>
+        <v>1.925145</v>
       </c>
       <c r="H8" t="n">
-        <v>2.335248</v>
+        <v>2.335239</v>
       </c>
       <c r="I8" t="n">
-        <v>2.843317</v>
+        <v>2.843292</v>
       </c>
       <c r="J8" t="n">
         <v>4.537561</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.299157</v>
+        <v>1.299158</v>
       </c>
       <c r="F9" t="n">
-        <v>1.454816</v>
+        <v>1.454818</v>
       </c>
       <c r="G9" t="n">
-        <v>1.352537</v>
+        <v>1.352542</v>
       </c>
       <c r="H9" t="n">
-        <v>1.317538</v>
+        <v>1.317546</v>
       </c>
       <c r="I9" t="n">
-        <v>1.35846</v>
+        <v>1.358477</v>
       </c>
       <c r="J9" t="n">
         <v>0.255876</v>
@@ -1137,16 +1137,16 @@
         <v>0.358602</v>
       </c>
       <c r="F10" t="n">
-        <v>0.47086</v>
+        <v>0.470858</v>
       </c>
       <c r="G10" t="n">
-        <v>0.501331</v>
+        <v>0.501327</v>
       </c>
       <c r="H10" t="n">
-        <v>0.553877</v>
+        <v>0.553868</v>
       </c>
       <c r="I10" t="n">
-        <v>0.633432</v>
+        <v>0.633406</v>
       </c>
       <c r="J10" t="n">
         <v>2.295868</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.000385</v>
+        <v>7.000388</v>
       </c>
       <c r="F11" t="n">
-        <v>9.773160000000001</v>
+        <v>9.773168999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>11.5973</v>
+        <v>11.597317</v>
       </c>
       <c r="H11" t="n">
-        <v>13.995431</v>
+        <v>13.995468</v>
       </c>
       <c r="I11" t="n">
-        <v>17.028378</v>
+        <v>17.028475</v>
       </c>
       <c r="J11" t="n">
         <v>11.020423</v>
@@ -1289,16 +1289,16 @@
         <v>0.264838</v>
       </c>
       <c r="F12" t="n">
-        <v>0.383829</v>
+        <v>0.383828</v>
       </c>
       <c r="G12" t="n">
-        <v>0.480593</v>
+        <v>0.480591</v>
       </c>
       <c r="H12" t="n">
-        <v>0.602549</v>
+        <v>0.602544</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7508</v>
+        <v>0.750787</v>
       </c>
       <c r="J12" t="n">
         <v>1.638447</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.74506</v>
+        <v>1.745059</v>
       </c>
       <c r="F13" t="n">
-        <v>2.444711</v>
+        <v>2.444707</v>
       </c>
       <c r="G13" t="n">
-        <v>2.828548</v>
+        <v>2.828537</v>
       </c>
       <c r="H13" t="n">
-        <v>3.358173</v>
+        <v>3.358148</v>
       </c>
       <c r="I13" t="n">
-        <v>4.111815</v>
+        <v>4.11174</v>
       </c>
       <c r="J13" t="n">
         <v>9.34281</v>
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>44.334686</v>
+        <v>44.334726</v>
       </c>
       <c r="F14" t="n">
-        <v>50.010891</v>
+        <v>50.010971</v>
       </c>
       <c r="G14" t="n">
-        <v>57.735685</v>
+        <v>57.735818</v>
       </c>
       <c r="H14" t="n">
-        <v>65.688772</v>
+        <v>65.688969</v>
       </c>
       <c r="I14" t="n">
-        <v>73.468909</v>
+        <v>73.469173</v>
       </c>
       <c r="J14" t="n">
-        <v>75.006755</v>
+        <v>75.007062</v>
       </c>
       <c r="K14" t="n">
-        <v>74.998142</v>
+        <v>74.99848</v>
       </c>
       <c r="L14" t="n">
-        <v>73.32784100000001</v>
+        <v>73.328197</v>
       </c>
       <c r="M14" t="n">
-        <v>73.23630799999999</v>
+        <v>73.23669</v>
       </c>
       <c r="N14" t="n">
-        <v>72.668706</v>
+        <v>72.669113</v>
       </c>
       <c r="O14" t="n">
-        <v>69.884134</v>
+        <v>69.88455399999999</v>
       </c>
       <c r="P14" t="n">
-        <v>66.729832</v>
+        <v>66.730265</v>
       </c>
       <c r="Q14" t="n">
-        <v>65.117779</v>
+        <v>65.118239</v>
       </c>
       <c r="R14" t="n">
-        <v>63.01669</v>
+        <v>63.017184</v>
       </c>
       <c r="S14" t="n">
-        <v>61.333467</v>
+        <v>61.334012</v>
       </c>
       <c r="T14" t="n">
-        <v>59.589742</v>
+        <v>59.590357</v>
       </c>
       <c r="U14" t="n">
-        <v>58.45851</v>
+        <v>58.459232</v>
       </c>
       <c r="V14" t="n">
-        <v>56.835875</v>
+        <v>56.836752</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64.377864</v>
+        <v>64.377835</v>
       </c>
       <c r="F15" t="n">
-        <v>79.40358999999999</v>
+        <v>79.403547</v>
       </c>
       <c r="G15" t="n">
-        <v>95.106897</v>
+        <v>95.106848</v>
       </c>
       <c r="H15" t="n">
-        <v>109.680369</v>
+        <v>109.680314</v>
       </c>
       <c r="I15" t="n">
-        <v>123.088655</v>
+        <v>123.088588</v>
       </c>
       <c r="J15" t="n">
-        <v>125.56917</v>
+        <v>125.569089</v>
       </c>
       <c r="K15" t="n">
-        <v>125.55338</v>
+        <v>125.553282</v>
       </c>
       <c r="L15" t="n">
-        <v>123.248206</v>
+        <v>123.248092</v>
       </c>
       <c r="M15" t="n">
-        <v>124.283643</v>
+        <v>124.283507</v>
       </c>
       <c r="N15" t="n">
-        <v>125.151158</v>
+        <v>125.150998</v>
       </c>
       <c r="O15" t="n">
-        <v>122.515015</v>
+        <v>122.514831</v>
       </c>
       <c r="P15" t="n">
-        <v>119.169304</v>
+        <v>119.169092</v>
       </c>
       <c r="Q15" t="n">
-        <v>118.278079</v>
+        <v>118.277827</v>
       </c>
       <c r="R15" t="n">
-        <v>116.105576</v>
+        <v>116.105278</v>
       </c>
       <c r="S15" t="n">
-        <v>114.283194</v>
+        <v>114.282834</v>
       </c>
       <c r="T15" t="n">
-        <v>111.896433</v>
+        <v>111.895993</v>
       </c>
       <c r="U15" t="n">
-        <v>110.231983</v>
+        <v>110.231425</v>
       </c>
       <c r="V15" t="n">
-        <v>107.259849</v>
+        <v>107.259117</v>
       </c>
     </row>
     <row r="16">
@@ -1590,58 +1590,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14.707327</v>
+        <v>14.707356</v>
       </c>
       <c r="F16" t="n">
-        <v>14.375654</v>
+        <v>14.375701</v>
       </c>
       <c r="G16" t="n">
-        <v>13.905316</v>
+        <v>13.90537</v>
       </c>
       <c r="H16" t="n">
-        <v>13.781657</v>
+        <v>13.781712</v>
       </c>
       <c r="I16" t="n">
-        <v>14.042032</v>
+        <v>14.042086</v>
       </c>
       <c r="J16" t="n">
-        <v>13.549329</v>
+        <v>13.549378</v>
       </c>
       <c r="K16" t="n">
-        <v>13.164083</v>
+        <v>13.164129</v>
       </c>
       <c r="L16" t="n">
-        <v>12.761281</v>
+        <v>12.761326</v>
       </c>
       <c r="M16" t="n">
-        <v>12.828081</v>
+        <v>12.828128</v>
       </c>
       <c r="N16" t="n">
-        <v>12.922265</v>
+        <v>12.922317</v>
       </c>
       <c r="O16" t="n">
-        <v>12.661689</v>
+        <v>12.661746</v>
       </c>
       <c r="P16" t="n">
-        <v>12.311939</v>
+        <v>12.311999</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.258772</v>
+        <v>12.258839</v>
       </c>
       <c r="R16" t="n">
-        <v>12.175646</v>
+        <v>12.175724</v>
       </c>
       <c r="S16" t="n">
-        <v>12.247351</v>
+        <v>12.247447</v>
       </c>
       <c r="T16" t="n">
-        <v>12.352183</v>
+        <v>12.352306</v>
       </c>
       <c r="U16" t="n">
-        <v>12.604085</v>
+        <v>12.60425</v>
       </c>
       <c r="V16" t="n">
-        <v>12.736471</v>
+        <v>12.736697</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16.43958</v>
+        <v>16.439543</v>
       </c>
       <c r="F17" t="n">
-        <v>18.710629</v>
+        <v>18.710549</v>
       </c>
       <c r="G17" t="n">
-        <v>21.06374</v>
+        <v>21.063609</v>
       </c>
       <c r="H17" t="n">
-        <v>23.045395</v>
+        <v>23.045213</v>
       </c>
       <c r="I17" t="n">
-        <v>24.721556</v>
+        <v>24.721324</v>
       </c>
       <c r="J17" t="n">
-        <v>24.139852</v>
+        <v>24.139595</v>
       </c>
       <c r="K17" t="n">
-        <v>23.224134</v>
+        <v>23.223861</v>
       </c>
       <c r="L17" t="n">
-        <v>22.149812</v>
+        <v>22.149532</v>
       </c>
       <c r="M17" t="n">
-        <v>21.998206</v>
+        <v>21.997917</v>
       </c>
       <c r="N17" t="n">
-        <v>22.059419</v>
+        <v>22.059124</v>
       </c>
       <c r="O17" t="n">
-        <v>22.064657</v>
+        <v>22.064373</v>
       </c>
       <c r="P17" t="n">
-        <v>22.259964</v>
+        <v>22.259699</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.988353</v>
+        <v>22.988101</v>
       </c>
       <c r="R17" t="n">
-        <v>23.302196</v>
+        <v>23.301957</v>
       </c>
       <c r="S17" t="n">
-        <v>23.506767</v>
+        <v>23.50653</v>
       </c>
       <c r="T17" t="n">
-        <v>23.459831</v>
+        <v>23.459588</v>
       </c>
       <c r="U17" t="n">
-        <v>23.496549</v>
+        <v>23.496288</v>
       </c>
       <c r="V17" t="n">
-        <v>23.231458</v>
+        <v>23.231164</v>
       </c>
     </row>
     <row r="18">
@@ -1742,58 +1742,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.260724</v>
+        <v>8.260721</v>
       </c>
       <c r="F18" t="n">
-        <v>9.832682</v>
+        <v>9.832678</v>
       </c>
       <c r="G18" t="n">
-        <v>10.95993</v>
+        <v>10.959923</v>
       </c>
       <c r="H18" t="n">
-        <v>11.854137</v>
+        <v>11.854124</v>
       </c>
       <c r="I18" t="n">
-        <v>12.766468</v>
+        <v>12.766449</v>
       </c>
       <c r="J18" t="n">
-        <v>12.881319</v>
+        <v>12.881301</v>
       </c>
       <c r="K18" t="n">
-        <v>12.915124</v>
+        <v>12.915111</v>
       </c>
       <c r="L18" t="n">
-        <v>12.757181</v>
+        <v>12.757173</v>
       </c>
       <c r="M18" t="n">
-        <v>12.79638</v>
+        <v>12.796376</v>
       </c>
       <c r="N18" t="n">
-        <v>12.586943</v>
+        <v>12.586938</v>
       </c>
       <c r="O18" t="n">
-        <v>11.838402</v>
+        <v>11.838393</v>
       </c>
       <c r="P18" t="n">
-        <v>10.968004</v>
+        <v>10.967988</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.362082</v>
+        <v>10.362058</v>
       </c>
       <c r="R18" t="n">
-        <v>9.727123000000001</v>
+        <v>9.727088999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>9.226573999999999</v>
+        <v>9.22653</v>
       </c>
       <c r="T18" t="n">
-        <v>8.792889000000001</v>
+        <v>8.792833999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>8.54609</v>
+        <v>8.546022000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>8.317095999999999</v>
+        <v>8.317017</v>
       </c>
     </row>
     <row r="19">
@@ -1818,58 +1818,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.891005</v>
+        <v>8.891006000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>12.425948</v>
+        <v>12.425951</v>
       </c>
       <c r="G19" t="n">
-        <v>15.168287</v>
+        <v>15.168293</v>
       </c>
       <c r="H19" t="n">
-        <v>18.358655</v>
+        <v>18.358663</v>
       </c>
       <c r="I19" t="n">
-        <v>22.09915</v>
+        <v>22.099162</v>
       </c>
       <c r="J19" t="n">
-        <v>22.559175</v>
+        <v>22.559189</v>
       </c>
       <c r="K19" t="n">
-        <v>22.512745</v>
+        <v>22.51276</v>
       </c>
       <c r="L19" t="n">
-        <v>22.054002</v>
+        <v>22.054017</v>
       </c>
       <c r="M19" t="n">
-        <v>23.392369</v>
+        <v>23.392387</v>
       </c>
       <c r="N19" t="n">
-        <v>25.9239</v>
+        <v>25.923922</v>
       </c>
       <c r="O19" t="n">
-        <v>28.939429</v>
+        <v>28.939455</v>
       </c>
       <c r="P19" t="n">
-        <v>32.502692</v>
+        <v>32.502724</v>
       </c>
       <c r="Q19" t="n">
-        <v>38.64908</v>
+        <v>38.649121</v>
       </c>
       <c r="R19" t="n">
-        <v>44.274248</v>
+        <v>44.274299</v>
       </c>
       <c r="S19" t="n">
-        <v>48.600639</v>
+        <v>48.600702</v>
       </c>
       <c r="T19" t="n">
-        <v>50.797788</v>
+        <v>50.797863</v>
       </c>
       <c r="U19" t="n">
-        <v>50.599201</v>
+        <v>50.599288</v>
       </c>
       <c r="V19" t="n">
-        <v>50.530714</v>
+        <v>50.530819</v>
       </c>
     </row>
     <row r="20">
@@ -1897,55 +1897,55 @@
         <v>1.903968</v>
       </c>
       <c r="F20" t="n">
-        <v>2.546414</v>
+        <v>2.546415</v>
       </c>
       <c r="G20" t="n">
-        <v>3.16313</v>
+        <v>3.163132</v>
       </c>
       <c r="H20" t="n">
-        <v>3.850525</v>
+        <v>3.850528</v>
       </c>
       <c r="I20" t="n">
-        <v>4.577688</v>
+        <v>4.577692</v>
       </c>
       <c r="J20" t="n">
-        <v>4.510536</v>
+        <v>4.510541</v>
       </c>
       <c r="K20" t="n">
-        <v>4.262886</v>
+        <v>4.262891</v>
       </c>
       <c r="L20" t="n">
-        <v>3.896543</v>
+        <v>3.896548</v>
       </c>
       <c r="M20" t="n">
-        <v>3.833029</v>
+        <v>3.833034</v>
       </c>
       <c r="N20" t="n">
-        <v>3.939981</v>
+        <v>3.939987</v>
       </c>
       <c r="O20" t="n">
-        <v>4.089462</v>
+        <v>4.089468</v>
       </c>
       <c r="P20" t="n">
-        <v>4.270491</v>
+        <v>4.270499</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.70981</v>
+        <v>4.709818</v>
       </c>
       <c r="R20" t="n">
-        <v>4.978333</v>
+        <v>4.978343</v>
       </c>
       <c r="S20" t="n">
-        <v>5.01337</v>
+        <v>5.013381</v>
       </c>
       <c r="T20" t="n">
-        <v>4.790585</v>
+        <v>4.790596</v>
       </c>
       <c r="U20" t="n">
-        <v>4.355381</v>
+        <v>4.355392</v>
       </c>
       <c r="V20" t="n">
-        <v>3.968134</v>
+        <v>3.968147</v>
       </c>
     </row>
     <row r="21">
@@ -1988,40 +1988,40 @@
         <v>0.242034</v>
       </c>
       <c r="K21" t="n">
-        <v>0.236119</v>
+        <v>0.236118</v>
       </c>
       <c r="L21" t="n">
-        <v>0.226035</v>
+        <v>0.226034</v>
       </c>
       <c r="M21" t="n">
-        <v>0.235212</v>
+        <v>0.235211</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2575</v>
+        <v>0.257499</v>
       </c>
       <c r="O21" t="n">
-        <v>0.286332</v>
+        <v>0.286331</v>
       </c>
       <c r="P21" t="n">
-        <v>0.322291</v>
+        <v>0.32229</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.38452</v>
+        <v>0.384518</v>
       </c>
       <c r="R21" t="n">
-        <v>0.439696</v>
+        <v>0.439694</v>
       </c>
       <c r="S21" t="n">
-        <v>0.486566</v>
+        <v>0.486564</v>
       </c>
       <c r="T21" t="n">
-        <v>0.514158</v>
+        <v>0.5141559999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5154840000000001</v>
+        <v>0.515482</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5127</v>
+        <v>0.512697</v>
       </c>
     </row>
     <row r="22">
@@ -2049,55 +2049,55 @@
         <v>1.73473</v>
       </c>
       <c r="F22" t="n">
-        <v>2.450657</v>
+        <v>2.450656</v>
       </c>
       <c r="G22" t="n">
-        <v>3.015387</v>
+        <v>3.015385</v>
       </c>
       <c r="H22" t="n">
-        <v>3.645858</v>
+        <v>3.645854</v>
       </c>
       <c r="I22" t="n">
-        <v>4.373811</v>
+        <v>4.373805</v>
       </c>
       <c r="J22" t="n">
-        <v>4.458843</v>
+        <v>4.458837</v>
       </c>
       <c r="K22" t="n">
-        <v>4.458518</v>
+        <v>4.458511</v>
       </c>
       <c r="L22" t="n">
-        <v>4.379287</v>
+        <v>4.37928</v>
       </c>
       <c r="M22" t="n">
-        <v>4.66378</v>
+        <v>4.663771</v>
       </c>
       <c r="N22" t="n">
-        <v>5.203758</v>
+        <v>5.203748</v>
       </c>
       <c r="O22" t="n">
-        <v>5.878822</v>
+        <v>5.87881</v>
       </c>
       <c r="P22" t="n">
-        <v>6.699919</v>
+        <v>6.699904</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.127297</v>
+        <v>8.127279</v>
       </c>
       <c r="R22" t="n">
-        <v>9.531212999999999</v>
+        <v>9.53119</v>
       </c>
       <c r="S22" t="n">
-        <v>10.72883</v>
+        <v>10.728802</v>
       </c>
       <c r="T22" t="n">
-        <v>11.499709</v>
+        <v>11.499677</v>
       </c>
       <c r="U22" t="n">
-        <v>11.729159</v>
+        <v>11.729122</v>
       </c>
       <c r="V22" t="n">
-        <v>11.970532</v>
+        <v>11.970489</v>
       </c>
     </row>
     <row r="23">
@@ -2122,58 +2122,58 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.316208</v>
+        <v>1.316207</v>
       </c>
       <c r="F23" t="n">
         <v>1.957611</v>
       </c>
       <c r="G23" t="n">
-        <v>2.598442</v>
+        <v>2.598441</v>
       </c>
       <c r="H23" t="n">
-        <v>3.460582</v>
+        <v>3.46058</v>
       </c>
       <c r="I23" t="n">
-        <v>4.584485</v>
+        <v>4.584483</v>
       </c>
       <c r="J23" t="n">
-        <v>5.105138</v>
+        <v>5.105135</v>
       </c>
       <c r="K23" t="n">
-        <v>5.49289</v>
+        <v>5.492886</v>
       </c>
       <c r="L23" t="n">
-        <v>5.755031</v>
+        <v>5.755027</v>
       </c>
       <c r="M23" t="n">
-        <v>6.497082</v>
+        <v>6.497078</v>
       </c>
       <c r="N23" t="n">
-        <v>7.633843</v>
+        <v>7.633838</v>
       </c>
       <c r="O23" t="n">
-        <v>9.022068000000001</v>
+        <v>9.022061000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>10.707183</v>
+        <v>10.707175</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.412066</v>
+        <v>13.412056</v>
       </c>
       <c r="R23" t="n">
-        <v>16.1256</v>
+        <v>16.125588</v>
       </c>
       <c r="S23" t="n">
-        <v>18.522207</v>
+        <v>18.522193</v>
       </c>
       <c r="T23" t="n">
-        <v>20.223638</v>
+        <v>20.223621</v>
       </c>
       <c r="U23" t="n">
-        <v>21.014516</v>
+        <v>21.014497</v>
       </c>
       <c r="V23" t="n">
-        <v>21.86655</v>
+        <v>21.866529</v>
       </c>
     </row>
     <row r="24">
@@ -2204,52 +2204,52 @@
         <v>1.463238</v>
       </c>
       <c r="G24" t="n">
-        <v>1.755224</v>
+        <v>1.755225</v>
       </c>
       <c r="H24" t="n">
-        <v>2.085431</v>
+        <v>2.085432</v>
       </c>
       <c r="I24" t="n">
-        <v>2.447081</v>
+        <v>2.447083</v>
       </c>
       <c r="J24" t="n">
-        <v>2.420211</v>
+        <v>2.420213</v>
       </c>
       <c r="K24" t="n">
-        <v>2.32308</v>
+        <v>2.323082</v>
       </c>
       <c r="L24" t="n">
-        <v>2.169909</v>
+        <v>2.169911</v>
       </c>
       <c r="M24" t="n">
-        <v>2.18028</v>
+        <v>2.180282</v>
       </c>
       <c r="N24" t="n">
-        <v>2.278192</v>
+        <v>2.278194</v>
       </c>
       <c r="O24" t="n">
-        <v>2.391963</v>
+        <v>2.391966</v>
       </c>
       <c r="P24" t="n">
-        <v>2.519192</v>
+        <v>2.519195</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.799773</v>
+        <v>2.799777</v>
       </c>
       <c r="R24" t="n">
-        <v>2.97931</v>
+        <v>2.979313</v>
       </c>
       <c r="S24" t="n">
-        <v>3.018458</v>
+        <v>3.018462</v>
       </c>
       <c r="T24" t="n">
-        <v>2.899675</v>
+        <v>2.899679</v>
       </c>
       <c r="U24" t="n">
-        <v>2.651766</v>
+        <v>2.65177</v>
       </c>
       <c r="V24" t="n">
-        <v>2.443269</v>
+        <v>2.443273</v>
       </c>
     </row>
     <row r="25">
@@ -2289,7 +2289,7 @@
         <v>0.527297</v>
       </c>
       <c r="J25" t="n">
-        <v>0.530266</v>
+        <v>0.530267</v>
       </c>
       <c r="K25" t="n">
         <v>0.517385</v>
@@ -2307,7 +2307,7 @@
         <v>0.5749379999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>0.616814</v>
+        <v>0.616815</v>
       </c>
       <c r="Q25" t="n">
         <v>0.697142</v>
@@ -2350,58 +2350,58 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3.546843</v>
+        <v>3.546841</v>
       </c>
       <c r="F26" t="n">
-        <v>4.749677</v>
+        <v>4.749673</v>
       </c>
       <c r="G26" t="n">
-        <v>5.452453</v>
+        <v>5.452447</v>
       </c>
       <c r="H26" t="n">
-        <v>6.238878</v>
+        <v>6.238868</v>
       </c>
       <c r="I26" t="n">
-        <v>7.157858</v>
+        <v>7.157843</v>
       </c>
       <c r="J26" t="n">
-        <v>7.018542</v>
+        <v>7.018523</v>
       </c>
       <c r="K26" t="n">
-        <v>6.789141</v>
+        <v>6.78912</v>
       </c>
       <c r="L26" t="n">
-        <v>6.506644</v>
+        <v>6.50662</v>
       </c>
       <c r="M26" t="n">
-        <v>6.800362</v>
+        <v>6.800334</v>
       </c>
       <c r="N26" t="n">
-        <v>7.457613</v>
+        <v>7.457579</v>
       </c>
       <c r="O26" t="n">
-        <v>8.283160000000001</v>
+        <v>8.283118</v>
       </c>
       <c r="P26" t="n">
-        <v>9.304928</v>
+        <v>9.304876</v>
       </c>
       <c r="Q26" t="n">
-        <v>11.115621</v>
+        <v>11.115552</v>
       </c>
       <c r="R26" t="n">
-        <v>12.840421</v>
+        <v>12.840333</v>
       </c>
       <c r="S26" t="n">
-        <v>14.271763</v>
+        <v>14.271655</v>
       </c>
       <c r="T26" t="n">
-        <v>15.178266</v>
+        <v>15.178136</v>
       </c>
       <c r="U26" t="n">
-        <v>15.441785</v>
+        <v>15.441633</v>
       </c>
       <c r="V26" t="n">
-        <v>15.798227</v>
+        <v>15.798041</v>
       </c>
     </row>
     <row r="27">
@@ -2429,55 +2429,55 @@
         <v>1.429116</v>
       </c>
       <c r="F27" t="n">
-        <v>1.987742</v>
+        <v>1.987741</v>
       </c>
       <c r="G27" t="n">
-        <v>2.36229</v>
+        <v>2.362288</v>
       </c>
       <c r="H27" t="n">
-        <v>2.821537</v>
+        <v>2.821534</v>
       </c>
       <c r="I27" t="n">
-        <v>3.413887</v>
+        <v>3.413883</v>
       </c>
       <c r="J27" t="n">
-        <v>3.542127</v>
+        <v>3.542122</v>
       </c>
       <c r="K27" t="n">
-        <v>3.605138</v>
+        <v>3.605132</v>
       </c>
       <c r="L27" t="n">
-        <v>3.602003</v>
+        <v>3.601996</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8938</v>
+        <v>3.893792</v>
       </c>
       <c r="N27" t="n">
-        <v>4.383297</v>
+        <v>4.383287</v>
       </c>
       <c r="O27" t="n">
-        <v>4.95056</v>
+        <v>4.950548</v>
       </c>
       <c r="P27" t="n">
-        <v>5.600838</v>
+        <v>5.600823</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.697482</v>
+        <v>6.697462</v>
       </c>
       <c r="R27" t="n">
-        <v>7.698076</v>
+        <v>7.698051</v>
       </c>
       <c r="S27" t="n">
-        <v>8.460929999999999</v>
+        <v>8.460899</v>
       </c>
       <c r="T27" t="n">
-        <v>8.831388</v>
+        <v>8.831348999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>8.757288000000001</v>
+        <v>8.757243000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>8.679001</v>
+        <v>8.678945000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2505,55 +2505,55 @@
         <v>3.408786</v>
       </c>
       <c r="F28" t="n">
-        <v>4.305058</v>
+        <v>4.30506</v>
       </c>
       <c r="G28" t="n">
-        <v>5.604917</v>
+        <v>5.604921</v>
       </c>
       <c r="H28" t="n">
-        <v>7.67185</v>
+        <v>7.671857</v>
       </c>
       <c r="I28" t="n">
-        <v>10.490396</v>
+        <v>10.490406</v>
       </c>
       <c r="J28" t="n">
-        <v>11.88173</v>
+        <v>11.881744</v>
       </c>
       <c r="K28" t="n">
-        <v>12.761315</v>
+        <v>12.761332</v>
       </c>
       <c r="L28" t="n">
-        <v>13.132854</v>
+        <v>13.132874</v>
       </c>
       <c r="M28" t="n">
-        <v>14.428532</v>
+        <v>14.428556</v>
       </c>
       <c r="N28" t="n">
-        <v>16.433441</v>
+        <v>16.433472</v>
       </c>
       <c r="O28" t="n">
-        <v>18.844098</v>
+        <v>18.844136</v>
       </c>
       <c r="P28" t="n">
-        <v>21.779323</v>
+        <v>21.779371</v>
       </c>
       <c r="Q28" t="n">
-        <v>26.680648</v>
+        <v>26.680713</v>
       </c>
       <c r="R28" t="n">
-        <v>31.391595</v>
+        <v>31.39168</v>
       </c>
       <c r="S28" t="n">
-        <v>35.247042</v>
+        <v>35.247148</v>
       </c>
       <c r="T28" t="n">
-        <v>37.571075</v>
+        <v>37.571204</v>
       </c>
       <c r="U28" t="n">
-        <v>38.126042</v>
+        <v>38.126195</v>
       </c>
       <c r="V28" t="n">
-        <v>38.813711</v>
+        <v>38.8139</v>
       </c>
     </row>
     <row r="29">
@@ -2587,7 +2587,7 @@
         <v>2.084478</v>
       </c>
       <c r="H29" t="n">
-        <v>2.621586</v>
+        <v>2.621587</v>
       </c>
       <c r="I29" t="n">
         <v>3.264375</v>
@@ -2599,37 +2599,37 @@
         <v>3.729309</v>
       </c>
       <c r="L29" t="n">
-        <v>4.039105</v>
+        <v>4.039106</v>
       </c>
       <c r="M29" t="n">
-        <v>4.572046</v>
+        <v>4.572047</v>
       </c>
       <c r="N29" t="n">
-        <v>5.211541</v>
+        <v>5.211543</v>
       </c>
       <c r="O29" t="n">
-        <v>5.897809</v>
+        <v>5.897811</v>
       </c>
       <c r="P29" t="n">
-        <v>6.74474</v>
+        <v>6.744743</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.900925</v>
+        <v>7.900929</v>
       </c>
       <c r="R29" t="n">
-        <v>9.115883999999999</v>
+        <v>9.115888999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>10.358147</v>
+        <v>10.358153</v>
       </c>
       <c r="T29" t="n">
-        <v>11.551229</v>
+        <v>11.551239</v>
       </c>
       <c r="U29" t="n">
-        <v>12.632375</v>
+        <v>12.632389</v>
       </c>
       <c r="V29" t="n">
-        <v>13.582842</v>
+        <v>13.582861</v>
       </c>
     </row>
     <row r="30">
@@ -2660,52 +2660,52 @@
         <v>1.049556</v>
       </c>
       <c r="G30" t="n">
-        <v>1.230655</v>
+        <v>1.230654</v>
       </c>
       <c r="H30" t="n">
-        <v>1.512699</v>
+        <v>1.512698</v>
       </c>
       <c r="I30" t="n">
-        <v>1.844694</v>
+        <v>1.844692</v>
       </c>
       <c r="J30" t="n">
-        <v>1.957367</v>
+        <v>1.957365</v>
       </c>
       <c r="K30" t="n">
-        <v>2.077774</v>
+        <v>2.077772</v>
       </c>
       <c r="L30" t="n">
-        <v>2.261433</v>
+        <v>2.26143</v>
       </c>
       <c r="M30" t="n">
-        <v>2.610486</v>
+        <v>2.610482</v>
       </c>
       <c r="N30" t="n">
-        <v>3.075056</v>
+        <v>3.075052</v>
       </c>
       <c r="O30" t="n">
-        <v>3.625529</v>
+        <v>3.625523</v>
       </c>
       <c r="P30" t="n">
-        <v>4.337053</v>
+        <v>4.337046</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.317792</v>
+        <v>5.317782</v>
       </c>
       <c r="R30" t="n">
-        <v>6.411391</v>
+        <v>6.411379</v>
       </c>
       <c r="S30" t="n">
-        <v>7.595059</v>
+        <v>7.595044</v>
       </c>
       <c r="T30" t="n">
-        <v>8.801349</v>
+        <v>8.801330999999999</v>
       </c>
       <c r="U30" t="n">
-        <v>10.023944</v>
+        <v>10.023921</v>
       </c>
       <c r="V30" t="n">
-        <v>11.254701</v>
+        <v>11.254673</v>
       </c>
     </row>
     <row r="31">
@@ -2736,7 +2736,7 @@
         <v>0.06825299999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.083064</v>
+        <v>0.083063</v>
       </c>
       <c r="H31" t="n">
         <v>0.102621</v>
@@ -2745,43 +2745,43 @@
         <v>0.125908</v>
       </c>
       <c r="J31" t="n">
-        <v>0.133394</v>
+        <v>0.133393</v>
       </c>
       <c r="K31" t="n">
-        <v>0.14063</v>
+        <v>0.140629</v>
       </c>
       <c r="L31" t="n">
-        <v>0.150252</v>
+        <v>0.150251</v>
       </c>
       <c r="M31" t="n">
-        <v>0.168425</v>
+        <v>0.168424</v>
       </c>
       <c r="N31" t="n">
-        <v>0.191365</v>
+        <v>0.191364</v>
       </c>
       <c r="O31" t="n">
-        <v>0.216978</v>
+        <v>0.216976</v>
       </c>
       <c r="P31" t="n">
-        <v>0.249487</v>
+        <v>0.249484</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.294499</v>
+        <v>0.294496</v>
       </c>
       <c r="R31" t="n">
-        <v>0.342581</v>
+        <v>0.342578</v>
       </c>
       <c r="S31" t="n">
-        <v>0.392319</v>
+        <v>0.392315</v>
       </c>
       <c r="T31" t="n">
-        <v>0.440355</v>
+        <v>0.44035</v>
       </c>
       <c r="U31" t="n">
-        <v>0.484136</v>
+        <v>0.484129</v>
       </c>
       <c r="V31" t="n">
-        <v>0.52271</v>
+        <v>0.5227000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2827,37 +2827,37 @@
         <v>5.990079</v>
       </c>
       <c r="L32" t="n">
-        <v>6.639782</v>
+        <v>6.639783</v>
       </c>
       <c r="M32" t="n">
-        <v>7.662516</v>
+        <v>7.662517</v>
       </c>
       <c r="N32" t="n">
-        <v>8.833106000000001</v>
+        <v>8.833107999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>10.033967</v>
+        <v>10.033969</v>
       </c>
       <c r="P32" t="n">
-        <v>11.439715</v>
+        <v>11.439719</v>
       </c>
       <c r="Q32" t="n">
-        <v>13.29176</v>
+        <v>13.291766</v>
       </c>
       <c r="R32" t="n">
-        <v>15.126232</v>
+        <v>15.12624</v>
       </c>
       <c r="S32" t="n">
-        <v>17.091213</v>
+        <v>17.091224</v>
       </c>
       <c r="T32" t="n">
-        <v>19.000052</v>
+        <v>19.000069</v>
       </c>
       <c r="U32" t="n">
-        <v>20.615023</v>
+        <v>20.615046</v>
       </c>
       <c r="V32" t="n">
-        <v>21.75959</v>
+        <v>21.759622</v>
       </c>
     </row>
     <row r="33">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.205711</v>
+        <v>2.20571</v>
       </c>
       <c r="F33" t="n">
         <v>2.635321</v>
@@ -2891,49 +2891,49 @@
         <v>3.264574</v>
       </c>
       <c r="H33" t="n">
-        <v>4.103009</v>
+        <v>4.103008</v>
       </c>
       <c r="I33" t="n">
-        <v>5.112617</v>
+        <v>5.112616</v>
       </c>
       <c r="J33" t="n">
         <v>5.458889</v>
       </c>
       <c r="K33" t="n">
-        <v>5.760749</v>
+        <v>5.760748</v>
       </c>
       <c r="L33" t="n">
-        <v>6.130657</v>
+        <v>6.130656</v>
       </c>
       <c r="M33" t="n">
-        <v>6.806388</v>
+        <v>6.806386</v>
       </c>
       <c r="N33" t="n">
-        <v>7.599159</v>
+        <v>7.599157</v>
       </c>
       <c r="O33" t="n">
-        <v>8.415525000000001</v>
+        <v>8.415523</v>
       </c>
       <c r="P33" t="n">
-        <v>9.396629000000001</v>
+        <v>9.396625999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>10.711231</v>
+        <v>10.711228</v>
       </c>
       <c r="R33" t="n">
-        <v>11.979218</v>
+        <v>11.979214</v>
       </c>
       <c r="S33" t="n">
-        <v>13.401458</v>
+        <v>13.401455</v>
       </c>
       <c r="T33" t="n">
-        <v>14.82403</v>
+        <v>14.824027</v>
       </c>
       <c r="U33" t="n">
-        <v>16.038056</v>
+        <v>16.038054</v>
       </c>
       <c r="V33" t="n">
-        <v>16.860207</v>
+        <v>16.860206</v>
       </c>
     </row>
     <row r="34">
@@ -2961,55 +2961,55 @@
         <v>0.8388600000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>1.759662</v>
+        <v>1.75966</v>
       </c>
       <c r="G34" t="n">
-        <v>3.694804</v>
+        <v>3.6948</v>
       </c>
       <c r="H34" t="n">
-        <v>6.712914</v>
+        <v>6.712908</v>
       </c>
       <c r="I34" t="n">
-        <v>10.576198</v>
+        <v>10.576189</v>
       </c>
       <c r="J34" t="n">
-        <v>12.978273</v>
+        <v>12.978261</v>
       </c>
       <c r="K34" t="n">
-        <v>14.818498</v>
+        <v>14.818482</v>
       </c>
       <c r="L34" t="n">
-        <v>16.464741</v>
+        <v>16.464721</v>
       </c>
       <c r="M34" t="n">
-        <v>18.660986</v>
+        <v>18.660961</v>
       </c>
       <c r="N34" t="n">
-        <v>21.079913</v>
+        <v>21.079883</v>
       </c>
       <c r="O34" t="n">
-        <v>23.573947</v>
+        <v>23.573909</v>
       </c>
       <c r="P34" t="n">
-        <v>26.637506</v>
+        <v>26.637459</v>
       </c>
       <c r="Q34" t="n">
-        <v>30.802908</v>
+        <v>30.802848</v>
       </c>
       <c r="R34" t="n">
-        <v>34.98173</v>
+        <v>34.981655</v>
       </c>
       <c r="S34" t="n">
-        <v>38.936557</v>
+        <v>38.936462</v>
       </c>
       <c r="T34" t="n">
-        <v>42.297358</v>
+        <v>42.297241</v>
       </c>
       <c r="U34" t="n">
-        <v>44.820496</v>
+        <v>44.82035</v>
       </c>
       <c r="V34" t="n">
-        <v>46.485637</v>
+        <v>46.48545</v>
       </c>
     </row>
     <row r="35">
@@ -3043,49 +3043,49 @@
         <v>3.041495</v>
       </c>
       <c r="H35" t="n">
-        <v>4.236605</v>
+        <v>4.236606</v>
       </c>
       <c r="I35" t="n">
-        <v>5.463254</v>
+        <v>5.463257</v>
       </c>
       <c r="J35" t="n">
-        <v>5.78819</v>
+        <v>5.788193</v>
       </c>
       <c r="K35" t="n">
-        <v>5.957047</v>
+        <v>5.95705</v>
       </c>
       <c r="L35" t="n">
-        <v>6.160158</v>
+        <v>6.160162</v>
       </c>
       <c r="M35" t="n">
-        <v>6.652272</v>
+        <v>6.652276</v>
       </c>
       <c r="N35" t="n">
-        <v>7.239136</v>
+        <v>7.239142</v>
       </c>
       <c r="O35" t="n">
-        <v>7.813332</v>
+        <v>7.813339</v>
       </c>
       <c r="P35" t="n">
-        <v>8.504122000000001</v>
+        <v>8.50413</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.452378</v>
+        <v>9.452387999999999</v>
       </c>
       <c r="R35" t="n">
-        <v>10.316731</v>
+        <v>10.316743</v>
       </c>
       <c r="S35" t="n">
-        <v>11.247857</v>
+        <v>11.247873</v>
       </c>
       <c r="T35" t="n">
-        <v>12.120563</v>
+        <v>12.120583</v>
       </c>
       <c r="U35" t="n">
-        <v>12.783197</v>
+        <v>12.783223</v>
       </c>
       <c r="V35" t="n">
-        <v>13.12219</v>
+        <v>13.122224</v>
       </c>
     </row>
     <row r="36">
@@ -3128,7 +3128,7 @@
         <v>0.269281</v>
       </c>
       <c r="K36" t="n">
-        <v>0.257573</v>
+        <v>0.257574</v>
       </c>
       <c r="L36" t="n">
         <v>0.251849</v>
@@ -3146,7 +3146,7 @@
         <v>0.292748</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.319343</v>
+        <v>0.319344</v>
       </c>
       <c r="R36" t="n">
         <v>0.343503</v>
@@ -3161,7 +3161,7 @@
         <v>0.391135</v>
       </c>
       <c r="V36" t="n">
-        <v>0.403872</v>
+        <v>0.403873</v>
       </c>
     </row>
     <row r="37">
@@ -3192,52 +3192,52 @@
         <v>1.643363</v>
       </c>
       <c r="G37" t="n">
-        <v>1.799816</v>
+        <v>1.799817</v>
       </c>
       <c r="H37" t="n">
         <v>2.041745</v>
       </c>
       <c r="I37" t="n">
-        <v>2.344554</v>
+        <v>2.344555</v>
       </c>
       <c r="J37" t="n">
-        <v>2.34297</v>
+        <v>2.342971</v>
       </c>
       <c r="K37" t="n">
-        <v>2.333666</v>
+        <v>2.333668</v>
       </c>
       <c r="L37" t="n">
-        <v>2.34975</v>
+        <v>2.349752</v>
       </c>
       <c r="M37" t="n">
-        <v>2.469549</v>
+        <v>2.469551</v>
       </c>
       <c r="N37" t="n">
-        <v>2.612702</v>
+        <v>2.612704</v>
       </c>
       <c r="O37" t="n">
-        <v>2.747434</v>
+        <v>2.747437</v>
       </c>
       <c r="P37" t="n">
-        <v>2.920336</v>
+        <v>2.920339</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.229225</v>
+        <v>3.229229</v>
       </c>
       <c r="R37" t="n">
-        <v>3.538469</v>
+        <v>3.538473</v>
       </c>
       <c r="S37" t="n">
-        <v>3.805125</v>
+        <v>3.805131</v>
       </c>
       <c r="T37" t="n">
-        <v>3.989359</v>
+        <v>3.989366</v>
       </c>
       <c r="U37" t="n">
-        <v>4.092662</v>
+        <v>4.092671</v>
       </c>
       <c r="V37" t="n">
-        <v>4.134792</v>
+        <v>4.134803</v>
       </c>
     </row>
     <row r="38">
@@ -3268,52 +3268,52 @@
         <v>4.606493</v>
       </c>
       <c r="G38" t="n">
-        <v>5.531312</v>
+        <v>5.531313</v>
       </c>
       <c r="H38" t="n">
-        <v>6.785727</v>
+        <v>6.785728</v>
       </c>
       <c r="I38" t="n">
-        <v>8.396065</v>
+        <v>8.396065999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>9.0878</v>
+        <v>9.087801000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>9.859365</v>
+        <v>9.859366</v>
       </c>
       <c r="L38" t="n">
-        <v>10.851092</v>
+        <v>10.851094</v>
       </c>
       <c r="M38" t="n">
-        <v>12.46938</v>
+        <v>12.469383</v>
       </c>
       <c r="N38" t="n">
-        <v>14.408982</v>
+        <v>14.408985</v>
       </c>
       <c r="O38" t="n">
-        <v>16.497223</v>
+        <v>16.497228</v>
       </c>
       <c r="P38" t="n">
-        <v>19.025011</v>
+        <v>19.025018</v>
       </c>
       <c r="Q38" t="n">
-        <v>22.384561</v>
+        <v>22.384571</v>
       </c>
       <c r="R38" t="n">
-        <v>25.783859</v>
+        <v>25.783873</v>
       </c>
       <c r="S38" t="n">
-        <v>29.056965</v>
+        <v>29.056984</v>
       </c>
       <c r="T38" t="n">
-        <v>31.915146</v>
+        <v>31.915173</v>
       </c>
       <c r="U38" t="n">
-        <v>34.159087</v>
+        <v>34.159123</v>
       </c>
       <c r="V38" t="n">
-        <v>35.766844</v>
+        <v>35.766893</v>
       </c>
     </row>
     <row r="39">
@@ -3362,34 +3362,34 @@
         <v>2.050842</v>
       </c>
       <c r="M39" t="n">
-        <v>2.297464</v>
+        <v>2.297463</v>
       </c>
       <c r="N39" t="n">
-        <v>2.569289</v>
+        <v>2.569288</v>
       </c>
       <c r="O39" t="n">
-        <v>2.83863</v>
+        <v>2.838629</v>
       </c>
       <c r="P39" t="n">
-        <v>3.166727</v>
+        <v>3.166726</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.62706</v>
+        <v>3.627058</v>
       </c>
       <c r="R39" t="n">
-        <v>4.102287</v>
+        <v>4.102286</v>
       </c>
       <c r="S39" t="n">
-        <v>4.581564</v>
+        <v>4.581562</v>
       </c>
       <c r="T39" t="n">
-        <v>5.071292</v>
+        <v>5.071291</v>
       </c>
       <c r="U39" t="n">
-        <v>5.542872</v>
+        <v>5.54287</v>
       </c>
       <c r="V39" t="n">
-        <v>5.971996</v>
+        <v>5.971995</v>
       </c>
     </row>
     <row r="40">
@@ -3453,19 +3453,19 @@
         <v>0.439177</v>
       </c>
       <c r="R40" t="n">
-        <v>0.508876</v>
+        <v>0.508875</v>
       </c>
       <c r="S40" t="n">
-        <v>0.581003</v>
+        <v>0.581002</v>
       </c>
       <c r="T40" t="n">
-        <v>0.649587</v>
+        <v>0.649586</v>
       </c>
       <c r="U40" t="n">
-        <v>0.710062</v>
+        <v>0.7100610000000001</v>
       </c>
       <c r="V40" t="n">
-        <v>0.760549</v>
+        <v>0.760548</v>
       </c>
     </row>
     <row r="41">
@@ -3496,7 +3496,7 @@
         <v>0.161602</v>
       </c>
       <c r="G41" t="n">
-        <v>0.204519</v>
+        <v>0.204518</v>
       </c>
       <c r="H41" t="n">
         <v>0.255277</v>
@@ -3508,7 +3508,7 @@
         <v>0.329639</v>
       </c>
       <c r="K41" t="n">
-        <v>0.343349</v>
+        <v>0.343348</v>
       </c>
       <c r="L41" t="n">
         <v>0.360273</v>
@@ -3520,28 +3520,28 @@
         <v>0.431383</v>
       </c>
       <c r="O41" t="n">
-        <v>0.467218</v>
+        <v>0.467217</v>
       </c>
       <c r="P41" t="n">
-        <v>0.5116039999999999</v>
+        <v>0.511603</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.575565</v>
+        <v>0.575563</v>
       </c>
       <c r="R41" t="n">
-        <v>0.639021</v>
+        <v>0.63902</v>
       </c>
       <c r="S41" t="n">
-        <v>0.698435</v>
+        <v>0.698433</v>
       </c>
       <c r="T41" t="n">
-        <v>0.747713</v>
+        <v>0.747711</v>
       </c>
       <c r="U41" t="n">
-        <v>0.782699</v>
+        <v>0.782697</v>
       </c>
       <c r="V41" t="n">
-        <v>0.802779</v>
+        <v>0.802776</v>
       </c>
     </row>
     <row r="42">
@@ -3569,55 +3569,55 @@
         <v>1.299276</v>
       </c>
       <c r="F42" t="n">
-        <v>1.474108</v>
+        <v>1.474109</v>
       </c>
       <c r="G42" t="n">
-        <v>1.698429</v>
+        <v>1.69843</v>
       </c>
       <c r="H42" t="n">
         <v>1.979649</v>
       </c>
       <c r="I42" t="n">
-        <v>2.297363</v>
+        <v>2.297365</v>
       </c>
       <c r="J42" t="n">
-        <v>2.308453</v>
+        <v>2.308454</v>
       </c>
       <c r="K42" t="n">
-        <v>2.313137</v>
+        <v>2.313138</v>
       </c>
       <c r="L42" t="n">
-        <v>2.34088</v>
+        <v>2.340881</v>
       </c>
       <c r="M42" t="n">
-        <v>2.470343</v>
+        <v>2.470344</v>
       </c>
       <c r="N42" t="n">
-        <v>2.631737</v>
+        <v>2.63174</v>
       </c>
       <c r="O42" t="n">
-        <v>2.788207</v>
+        <v>2.78821</v>
       </c>
       <c r="P42" t="n">
-        <v>2.983953</v>
+        <v>2.983956</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.265266</v>
+        <v>3.26527</v>
       </c>
       <c r="R42" t="n">
-        <v>3.509294</v>
+        <v>3.509298</v>
       </c>
       <c r="S42" t="n">
-        <v>3.702627</v>
+        <v>3.702632</v>
       </c>
       <c r="T42" t="n">
-        <v>3.824096</v>
+        <v>3.824103</v>
       </c>
       <c r="U42" t="n">
-        <v>3.86421</v>
+        <v>3.864218</v>
       </c>
       <c r="V42" t="n">
-        <v>3.833832</v>
+        <v>3.833842</v>
       </c>
     </row>
     <row r="43">
@@ -3657,43 +3657,43 @@
         <v>1.605171</v>
       </c>
       <c r="J43" t="n">
-        <v>1.956708</v>
+        <v>1.956709</v>
       </c>
       <c r="K43" t="n">
-        <v>2.326016</v>
+        <v>2.326017</v>
       </c>
       <c r="L43" t="n">
-        <v>2.726699</v>
+        <v>2.7267</v>
       </c>
       <c r="M43" t="n">
-        <v>3.272162</v>
+        <v>3.272163</v>
       </c>
       <c r="N43" t="n">
-        <v>3.90697</v>
+        <v>3.906971</v>
       </c>
       <c r="O43" t="n">
-        <v>4.591494</v>
+        <v>4.591496</v>
       </c>
       <c r="P43" t="n">
-        <v>5.407113</v>
+        <v>5.407116</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.472723</v>
+        <v>6.472727</v>
       </c>
       <c r="R43" t="n">
-        <v>7.585003</v>
+        <v>7.585009</v>
       </c>
       <c r="S43" t="n">
-        <v>8.703780999999999</v>
+        <v>8.70379</v>
       </c>
       <c r="T43" t="n">
-        <v>9.800169</v>
+        <v>9.800179999999999</v>
       </c>
       <c r="U43" t="n">
-        <v>10.830914</v>
+        <v>10.83093</v>
       </c>
       <c r="V43" t="n">
-        <v>11.771466</v>
+        <v>11.771489</v>
       </c>
     </row>
     <row r="44">
@@ -3724,52 +3724,52 @@
         <v>1.101247</v>
       </c>
       <c r="G44" t="n">
-        <v>1.507176</v>
+        <v>1.507175</v>
       </c>
       <c r="H44" t="n">
-        <v>2.095436</v>
+        <v>2.095435</v>
       </c>
       <c r="I44" t="n">
-        <v>2.846497</v>
+        <v>2.846496</v>
       </c>
       <c r="J44" t="n">
-        <v>3.238555</v>
+        <v>3.238553</v>
       </c>
       <c r="K44" t="n">
-        <v>3.583123</v>
+        <v>3.58312</v>
       </c>
       <c r="L44" t="n">
-        <v>3.948596</v>
+        <v>3.948593</v>
       </c>
       <c r="M44" t="n">
-        <v>4.49455</v>
+        <v>4.494546</v>
       </c>
       <c r="N44" t="n">
-        <v>5.107173</v>
+        <v>5.107167</v>
       </c>
       <c r="O44" t="n">
-        <v>5.726567</v>
+        <v>5.72656</v>
       </c>
       <c r="P44" t="n">
-        <v>6.467272</v>
+        <v>6.467264</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.470862</v>
+        <v>7.470852</v>
       </c>
       <c r="R44" t="n">
-        <v>8.495107000000001</v>
+        <v>8.495094</v>
       </c>
       <c r="S44" t="n">
-        <v>9.524196</v>
+        <v>9.524179999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>10.494746</v>
+        <v>10.494726</v>
       </c>
       <c r="U44" t="n">
-        <v>11.352669</v>
+        <v>11.352644</v>
       </c>
       <c r="V44" t="n">
-        <v>12.088498</v>
+        <v>12.088467</v>
       </c>
     </row>
     <row r="45">
@@ -3812,40 +3812,40 @@
         <v>1.732092</v>
       </c>
       <c r="K45" t="n">
-        <v>1.839752</v>
+        <v>1.839753</v>
       </c>
       <c r="L45" t="n">
-        <v>1.982307</v>
+        <v>1.982308</v>
       </c>
       <c r="M45" t="n">
-        <v>2.22159</v>
+        <v>2.221591</v>
       </c>
       <c r="N45" t="n">
-        <v>2.504602</v>
+        <v>2.504603</v>
       </c>
       <c r="O45" t="n">
-        <v>2.806279</v>
+        <v>2.80628</v>
       </c>
       <c r="P45" t="n">
-        <v>3.181966</v>
+        <v>3.181968</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.690997</v>
+        <v>3.690999</v>
       </c>
       <c r="R45" t="n">
-        <v>4.197577</v>
+        <v>4.19758</v>
       </c>
       <c r="S45" t="n">
-        <v>4.672201</v>
+        <v>4.672205</v>
       </c>
       <c r="T45" t="n">
-        <v>5.070371</v>
+        <v>5.070377</v>
       </c>
       <c r="U45" t="n">
-        <v>5.360956</v>
+        <v>5.360962</v>
       </c>
       <c r="V45" t="n">
-        <v>5.541289</v>
+        <v>5.541298</v>
       </c>
     </row>
     <row r="46">
@@ -3879,49 +3879,49 @@
         <v>0.987409</v>
       </c>
       <c r="H46" t="n">
-        <v>1.397657</v>
+        <v>1.397656</v>
       </c>
       <c r="I46" t="n">
-        <v>1.925945</v>
+        <v>1.925943</v>
       </c>
       <c r="J46" t="n">
-        <v>2.261582</v>
+        <v>2.26158</v>
       </c>
       <c r="K46" t="n">
-        <v>2.617113</v>
+        <v>2.617109</v>
       </c>
       <c r="L46" t="n">
-        <v>3.049705</v>
+        <v>3.049701</v>
       </c>
       <c r="M46" t="n">
-        <v>3.690373</v>
+        <v>3.690367</v>
       </c>
       <c r="N46" t="n">
-        <v>4.462129</v>
+        <v>4.462121</v>
       </c>
       <c r="O46" t="n">
-        <v>5.322906</v>
+        <v>5.322895</v>
       </c>
       <c r="P46" t="n">
-        <v>6.397035</v>
+        <v>6.397022</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.870488</v>
+        <v>7.870471</v>
       </c>
       <c r="R46" t="n">
-        <v>9.523948000000001</v>
+        <v>9.523925</v>
       </c>
       <c r="S46" t="n">
-        <v>11.324602</v>
+        <v>11.324572</v>
       </c>
       <c r="T46" t="n">
-        <v>13.171586</v>
+        <v>13.171549</v>
       </c>
       <c r="U46" t="n">
-        <v>14.958786</v>
+        <v>14.958738</v>
       </c>
       <c r="V46" t="n">
-        <v>16.635569</v>
+        <v>16.635507</v>
       </c>
     </row>
     <row r="47">
@@ -3946,58 +3946,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>28.26207</v>
+        <v>28.262071</v>
       </c>
       <c r="F47" t="n">
-        <v>39.706628</v>
+        <v>39.70663</v>
       </c>
       <c r="G47" t="n">
-        <v>53.06988</v>
+        <v>53.069884</v>
       </c>
       <c r="H47" t="n">
-        <v>70.027627</v>
+        <v>70.027635</v>
       </c>
       <c r="I47" t="n">
-        <v>91.254029</v>
+        <v>91.254041</v>
       </c>
       <c r="J47" t="n">
-        <v>102.803107</v>
+        <v>102.803123</v>
       </c>
       <c r="K47" t="n">
-        <v>115.143914</v>
+        <v>115.143935</v>
       </c>
       <c r="L47" t="n">
-        <v>129.839704</v>
+        <v>129.839729</v>
       </c>
       <c r="M47" t="n">
-        <v>151.182049</v>
+        <v>151.182081</v>
       </c>
       <c r="N47" t="n">
-        <v>174.527771</v>
+        <v>174.527813</v>
       </c>
       <c r="O47" t="n">
-        <v>196.865352</v>
+        <v>196.865404</v>
       </c>
       <c r="P47" t="n">
-        <v>221.012373</v>
+        <v>221.012436</v>
       </c>
       <c r="Q47" t="n">
-        <v>251.010979</v>
+        <v>251.011056</v>
       </c>
       <c r="R47" t="n">
-        <v>277.917579</v>
+        <v>277.917672</v>
       </c>
       <c r="S47" t="n">
-        <v>300.604252</v>
+        <v>300.604363</v>
       </c>
       <c r="T47" t="n">
-        <v>316.836917</v>
+        <v>316.837045</v>
       </c>
       <c r="U47" t="n">
-        <v>326.00391</v>
+        <v>326.004056</v>
       </c>
       <c r="V47" t="n">
-        <v>329.089992</v>
+        <v>329.090161</v>
       </c>
     </row>
     <row r="48">
@@ -4031,49 +4031,49 @@
         <v>3.329863</v>
       </c>
       <c r="H48" t="n">
-        <v>4.103648</v>
+        <v>4.103649</v>
       </c>
       <c r="I48" t="n">
-        <v>4.985886</v>
+        <v>4.985887</v>
       </c>
       <c r="J48" t="n">
-        <v>5.200127</v>
+        <v>5.200128</v>
       </c>
       <c r="K48" t="n">
-        <v>5.398648</v>
+        <v>5.398649</v>
       </c>
       <c r="L48" t="n">
-        <v>5.697203</v>
+        <v>5.697204</v>
       </c>
       <c r="M48" t="n">
-        <v>6.30722</v>
+        <v>6.307221</v>
       </c>
       <c r="N48" t="n">
-        <v>7.05151</v>
+        <v>7.051511</v>
       </c>
       <c r="O48" t="n">
-        <v>7.854503</v>
+        <v>7.854505</v>
       </c>
       <c r="P48" t="n">
-        <v>8.874656</v>
+        <v>8.874658</v>
       </c>
       <c r="Q48" t="n">
-        <v>10.307961</v>
+        <v>10.307964</v>
       </c>
       <c r="R48" t="n">
-        <v>11.827722</v>
+        <v>11.827727</v>
       </c>
       <c r="S48" t="n">
-        <v>13.396457</v>
+        <v>13.396465</v>
       </c>
       <c r="T48" t="n">
-        <v>14.900088</v>
+        <v>14.900098</v>
       </c>
       <c r="U48" t="n">
-        <v>16.235078</v>
+        <v>16.235093</v>
       </c>
       <c r="V48" t="n">
-        <v>17.349219</v>
+        <v>17.349239</v>
       </c>
     </row>
     <row r="49">
@@ -4107,49 +4107,49 @@
         <v>0.396417</v>
       </c>
       <c r="H49" t="n">
-        <v>0.49243</v>
+        <v>0.492429</v>
       </c>
       <c r="I49" t="n">
-        <v>0.60026</v>
+        <v>0.600259</v>
       </c>
       <c r="J49" t="n">
-        <v>0.631766</v>
+        <v>0.631765</v>
       </c>
       <c r="K49" t="n">
-        <v>0.664551</v>
+        <v>0.66455</v>
       </c>
       <c r="L49" t="n">
-        <v>0.712251</v>
+        <v>0.71225</v>
       </c>
       <c r="M49" t="n">
-        <v>0.801859</v>
+        <v>0.801857</v>
       </c>
       <c r="N49" t="n">
-        <v>0.91353</v>
+        <v>0.913528</v>
       </c>
       <c r="O49" t="n">
-        <v>1.034935</v>
+        <v>1.034933</v>
       </c>
       <c r="P49" t="n">
-        <v>1.183709</v>
+        <v>1.183706</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.384356</v>
+        <v>1.384352</v>
       </c>
       <c r="R49" t="n">
-        <v>1.600015</v>
+        <v>1.600011</v>
       </c>
       <c r="S49" t="n">
-        <v>1.827707</v>
+        <v>1.827701</v>
       </c>
       <c r="T49" t="n">
-        <v>2.052227</v>
+        <v>2.05222</v>
       </c>
       <c r="U49" t="n">
-        <v>2.255898</v>
+        <v>2.255889</v>
       </c>
       <c r="V49" t="n">
-        <v>2.429836</v>
+        <v>2.429825</v>
       </c>
     </row>
     <row r="50">
@@ -4256,52 +4256,52 @@
         <v>0.444004</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5274450000000001</v>
+        <v>0.527444</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6383219999999999</v>
+        <v>0.63832</v>
       </c>
       <c r="I51" t="n">
-        <v>0.776053</v>
+        <v>0.776052</v>
       </c>
       <c r="J51" t="n">
-        <v>0.820519</v>
+        <v>0.820516</v>
       </c>
       <c r="K51" t="n">
-        <v>0.866511</v>
+        <v>0.8665079999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>0.930429</v>
+        <v>0.9304249999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>1.050447</v>
+        <v>1.050442</v>
       </c>
       <c r="N51" t="n">
-        <v>1.201168</v>
+        <v>1.201163</v>
       </c>
       <c r="O51" t="n">
-        <v>1.368779</v>
+        <v>1.368772</v>
       </c>
       <c r="P51" t="n">
-        <v>1.579636</v>
+        <v>1.579627</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.870616</v>
+        <v>1.870605</v>
       </c>
       <c r="R51" t="n">
-        <v>2.179821</v>
+        <v>2.179807</v>
       </c>
       <c r="S51" t="n">
-        <v>2.499681</v>
+        <v>2.499662</v>
       </c>
       <c r="T51" t="n">
-        <v>2.809582</v>
+        <v>2.809559</v>
       </c>
       <c r="U51" t="n">
-        <v>3.093035</v>
+        <v>3.093005</v>
       </c>
       <c r="V51" t="n">
-        <v>3.34301</v>
+        <v>3.342971</v>
       </c>
     </row>
     <row r="52">
@@ -4332,7 +4332,7 @@
         <v>0.384409</v>
       </c>
       <c r="G52" t="n">
-        <v>0.411816</v>
+        <v>0.411815</v>
       </c>
       <c r="H52" t="n">
         <v>0.468296</v>
@@ -4344,40 +4344,40 @@
         <v>0.580844</v>
       </c>
       <c r="K52" t="n">
-        <v>0.622211</v>
+        <v>0.62221</v>
       </c>
       <c r="L52" t="n">
-        <v>0.6740390000000001</v>
+        <v>0.674038</v>
       </c>
       <c r="M52" t="n">
-        <v>0.7548550000000001</v>
+        <v>0.754854</v>
       </c>
       <c r="N52" t="n">
-        <v>0.846347</v>
+        <v>0.846346</v>
       </c>
       <c r="O52" t="n">
-        <v>0.941819</v>
+        <v>0.941818</v>
       </c>
       <c r="P52" t="n">
-        <v>1.063136</v>
+        <v>1.063134</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.237172</v>
+        <v>1.23717</v>
       </c>
       <c r="R52" t="n">
-        <v>1.427261</v>
+        <v>1.427259</v>
       </c>
       <c r="S52" t="n">
-        <v>1.63343</v>
+        <v>1.633428</v>
       </c>
       <c r="T52" t="n">
-        <v>1.848197</v>
+        <v>1.848194</v>
       </c>
       <c r="U52" t="n">
-        <v>2.066146</v>
+        <v>2.066143</v>
       </c>
       <c r="V52" t="n">
-        <v>2.285972</v>
+        <v>2.285968</v>
       </c>
     </row>
     <row r="53">
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>62.280897</v>
+        <v>62.280901</v>
       </c>
       <c r="F54" t="n">
-        <v>58.781853</v>
+        <v>58.781856</v>
       </c>
       <c r="G54" t="n">
-        <v>57.143028</v>
+        <v>57.143031</v>
       </c>
       <c r="H54" t="n">
-        <v>55.73351</v>
+        <v>55.733512</v>
       </c>
       <c r="I54" t="n">
-        <v>54.527685</v>
+        <v>54.527686</v>
       </c>
       <c r="J54" t="n">
         <v>51.825308</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>59.879527</v>
+        <v>59.879523</v>
       </c>
       <c r="F55" t="n">
-        <v>66.063546</v>
+        <v>66.063543</v>
       </c>
       <c r="G55" t="n">
-        <v>70.669203</v>
+        <v>70.6692</v>
       </c>
       <c r="H55" t="n">
-        <v>72.064144</v>
+        <v>72.064142</v>
       </c>
       <c r="I55" t="n">
-        <v>71.00892</v>
+        <v>71.00891900000001</v>
       </c>
       <c r="J55" t="n">
         <v>66.01529600000001</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.087233</v>
+        <v>0.134917</v>
       </c>
       <c r="F58" t="n">
-        <v>0.060498</v>
+        <v>0.095431</v>
       </c>
       <c r="G58" t="n">
-        <v>0.051058</v>
+        <v>0.07939599999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.044428</v>
+        <v>0.066747</v>
       </c>
       <c r="I58" t="n">
-        <v>0.03596</v>
+        <v>0.049782</v>
       </c>
       <c r="J58" t="n">
         <v>0.021093</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.069594</v>
+        <v>0.072215</v>
       </c>
       <c r="F59" t="n">
-        <v>0.07854800000000001</v>
+        <v>0.08018400000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.087214</v>
+        <v>0.08866300000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09850100000000001</v>
+        <v>0.099472</v>
       </c>
       <c r="I59" t="n">
-        <v>0.111579</v>
+        <v>0.111971</v>
       </c>
       <c r="J59" t="n">
         <v>0.116451</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.061766</v>
+        <v>0.091543</v>
       </c>
       <c r="F60" t="n">
-        <v>0.043813</v>
+        <v>0.060811</v>
       </c>
       <c r="G60" t="n">
-        <v>0.04273</v>
+        <v>0.053424</v>
       </c>
       <c r="H60" t="n">
-        <v>0.045617</v>
+        <v>0.052537</v>
       </c>
       <c r="I60" t="n">
-        <v>0.048069</v>
+        <v>0.051824</v>
       </c>
       <c r="J60" t="n">
         <v>0.044286</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.017864</v>
+        <v>1.284342</v>
       </c>
       <c r="F61" t="n">
-        <v>0.965994</v>
+        <v>1.157436</v>
       </c>
       <c r="G61" t="n">
-        <v>1.055098</v>
+        <v>1.197836</v>
       </c>
       <c r="H61" t="n">
-        <v>1.197842</v>
+        <v>1.29923</v>
       </c>
       <c r="I61" t="n">
-        <v>1.358638</v>
+        <v>1.415167</v>
       </c>
       <c r="J61" t="n">
         <v>1.395056</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2.923674</v>
+        <v>4.080251</v>
       </c>
       <c r="F62" t="n">
-        <v>2.234415</v>
+        <v>3.147845</v>
       </c>
       <c r="G62" t="n">
-        <v>1.933323</v>
+        <v>2.666656</v>
       </c>
       <c r="H62" t="n">
-        <v>1.723491</v>
+        <v>2.272017</v>
       </c>
       <c r="I62" t="n">
-        <v>1.504025</v>
+        <v>1.820808</v>
       </c>
       <c r="J62" t="n">
         <v>1.128272</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2.759055</v>
+        <v>3.634871</v>
       </c>
       <c r="F63" t="n">
-        <v>2.405716</v>
+        <v>3.076099</v>
       </c>
       <c r="G63" t="n">
-        <v>2.453521</v>
+        <v>2.965342</v>
       </c>
       <c r="H63" t="n">
-        <v>2.633284</v>
+        <v>3.006603</v>
       </c>
       <c r="I63" t="n">
-        <v>2.769288</v>
+        <v>2.991659</v>
       </c>
       <c r="J63" t="n">
         <v>2.554214</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.018907</v>
+        <v>0.022361</v>
       </c>
       <c r="F64" t="n">
-        <v>0.019472</v>
+        <v>0.021478</v>
       </c>
       <c r="G64" t="n">
-        <v>0.021351</v>
+        <v>0.022742</v>
       </c>
       <c r="H64" t="n">
-        <v>0.023192</v>
+        <v>0.024182</v>
       </c>
       <c r="I64" t="n">
-        <v>0.024871</v>
+        <v>0.025439</v>
       </c>
       <c r="J64" t="n">
         <v>0.024567</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.93268</v>
+        <v>5.093073</v>
       </c>
       <c r="F65" t="n">
-        <v>5.528021</v>
+        <v>5.659758</v>
       </c>
       <c r="G65" t="n">
-        <v>6.372868</v>
+        <v>6.480304</v>
       </c>
       <c r="H65" t="n">
-        <v>7.371505</v>
+        <v>7.448067</v>
       </c>
       <c r="I65" t="n">
-        <v>8.406827</v>
+        <v>8.447634000000001</v>
       </c>
       <c r="J65" t="n">
         <v>8.684742</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5.17906</v>
+        <v>4.948416</v>
       </c>
       <c r="F66" t="n">
-        <v>5.987914</v>
+        <v>5.814272</v>
       </c>
       <c r="G66" t="n">
-        <v>6.891676</v>
+        <v>6.746433</v>
       </c>
       <c r="H66" t="n">
-        <v>7.87324</v>
+        <v>7.749899</v>
       </c>
       <c r="I66" t="n">
-        <v>8.887539</v>
+        <v>8.803164000000001</v>
       </c>
       <c r="J66" t="n">
         <v>9.146428</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>25.079348</v>
+        <v>21.36588</v>
       </c>
       <c r="F67" t="n">
-        <v>27.65546</v>
+        <v>25.097045</v>
       </c>
       <c r="G67" t="n">
-        <v>27.862062</v>
+        <v>26.04952</v>
       </c>
       <c r="H67" t="n">
-        <v>27.596086</v>
+        <v>26.34416</v>
       </c>
       <c r="I67" t="n">
-        <v>27.337181</v>
+        <v>26.640908</v>
       </c>
       <c r="J67" t="n">
         <v>25.172457</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.877501</v>
+        <v>1.12767</v>
       </c>
       <c r="F68" t="n">
-        <v>0.733263</v>
+        <v>0.941758</v>
       </c>
       <c r="G68" t="n">
-        <v>0.652875</v>
+        <v>0.849264</v>
       </c>
       <c r="H68" t="n">
-        <v>0.583013</v>
+        <v>0.75309</v>
       </c>
       <c r="I68" t="n">
-        <v>0.500847</v>
+        <v>0.6104850000000001</v>
       </c>
       <c r="J68" t="n">
         <v>0.361292</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.026867</v>
+        <v>0.032644</v>
       </c>
       <c r="F69" t="n">
-        <v>0.026008</v>
+        <v>0.03002</v>
       </c>
       <c r="G69" t="n">
-        <v>0.028004</v>
+        <v>0.030992</v>
       </c>
       <c r="H69" t="n">
-        <v>0.030965</v>
+        <v>0.033088</v>
       </c>
       <c r="I69" t="n">
-        <v>0.034052</v>
+        <v>0.035239</v>
       </c>
       <c r="J69" t="n">
         <v>0.033656</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8.020208</v>
+        <v>7.071733</v>
       </c>
       <c r="F70" t="n">
-        <v>9.492665000000001</v>
+        <v>8.772294</v>
       </c>
       <c r="G70" t="n">
-        <v>10.602135</v>
+        <v>10.030087</v>
       </c>
       <c r="H70" t="n">
-        <v>11.545722</v>
+        <v>11.107443</v>
       </c>
       <c r="I70" t="n">
-        <v>12.269398</v>
+        <v>12.006571</v>
       </c>
       <c r="J70" t="n">
         <v>11.823443</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1.084484</v>
+        <v>1.496928</v>
       </c>
       <c r="F71" t="n">
-        <v>0.90123</v>
+        <v>1.243312</v>
       </c>
       <c r="G71" t="n">
-        <v>0.864231</v>
+        <v>1.140631</v>
       </c>
       <c r="H71" t="n">
-        <v>0.88151</v>
+        <v>1.088814</v>
       </c>
       <c r="I71" t="n">
-        <v>0.914204</v>
+        <v>1.034807</v>
       </c>
       <c r="J71" t="n">
         <v>0.844846</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2.061424</v>
+        <v>2.137699</v>
       </c>
       <c r="F72" t="n">
-        <v>2.280703</v>
+        <v>2.309056</v>
       </c>
       <c r="G72" t="n">
-        <v>2.549825</v>
+        <v>2.557563</v>
       </c>
       <c r="H72" t="n">
-        <v>2.775682</v>
+        <v>2.775324</v>
       </c>
       <c r="I72" t="n">
-        <v>2.927179</v>
+        <v>2.9259</v>
       </c>
       <c r="J72" t="n">
         <v>2.787935</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2.595936</v>
+        <v>4.199133</v>
       </c>
       <c r="F73" t="n">
-        <v>1.279848</v>
+        <v>2.184645</v>
       </c>
       <c r="G73" t="n">
-        <v>0.736436</v>
+        <v>1.243761</v>
       </c>
       <c r="H73" t="n">
-        <v>0.510843</v>
+        <v>0.812957</v>
       </c>
       <c r="I73" t="n">
-        <v>0.372215</v>
+        <v>0.529807</v>
       </c>
       <c r="J73" t="n">
         <v>0.203058</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.020948</v>
+        <v>0.022877</v>
       </c>
       <c r="F74" t="n">
-        <v>0.018228</v>
+        <v>0.020351</v>
       </c>
       <c r="G74" t="n">
-        <v>0.017989</v>
+        <v>0.019782</v>
       </c>
       <c r="H74" t="n">
-        <v>0.018938</v>
+        <v>0.020229</v>
       </c>
       <c r="I74" t="n">
-        <v>0.020179</v>
+        <v>0.020885</v>
       </c>
       <c r="J74" t="n">
         <v>0.019478</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2.380572</v>
+        <v>2.104348</v>
       </c>
       <c r="F75" t="n">
-        <v>2.678551</v>
+        <v>2.286636</v>
       </c>
       <c r="G75" t="n">
-        <v>2.861154</v>
+        <v>2.419142</v>
       </c>
       <c r="H75" t="n">
-        <v>3.000367</v>
+        <v>2.483035</v>
       </c>
       <c r="I75" t="n">
-        <v>3.369196</v>
+        <v>2.705564</v>
       </c>
       <c r="J75" t="n">
         <v>4.654843</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7.556497</v>
+        <v>9.191579000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>9.158628999999999</v>
+        <v>10.58938</v>
       </c>
       <c r="G76" t="n">
-        <v>9.530017000000001</v>
+        <v>10.016665</v>
       </c>
       <c r="H76" t="n">
-        <v>9.540982</v>
+        <v>9.170742000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>10.480471</v>
+        <v>9.26516</v>
       </c>
       <c r="J76" t="n">
         <v>13.874528</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3.76136</v>
+        <v>3.591411</v>
       </c>
       <c r="F77" t="n">
-        <v>4.177101</v>
+        <v>4.1278</v>
       </c>
       <c r="G77" t="n">
-        <v>4.555936</v>
+        <v>4.551289</v>
       </c>
       <c r="H77" t="n">
-        <v>4.524812</v>
+        <v>4.437499</v>
       </c>
       <c r="I77" t="n">
-        <v>4.510984</v>
+        <v>4.205694</v>
       </c>
       <c r="J77" t="n">
         <v>5.368072</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>39.628865</v>
+        <v>51.866082</v>
       </c>
       <c r="F78" t="n">
-        <v>41.980651</v>
+        <v>51.040676</v>
       </c>
       <c r="G78" t="n">
-        <v>43.135187</v>
+        <v>48.922908</v>
       </c>
       <c r="H78" t="n">
-        <v>41.035223</v>
+        <v>44.922421</v>
       </c>
       <c r="I78" t="n">
-        <v>38.323588</v>
+        <v>41.322885</v>
       </c>
       <c r="J78" t="n">
         <v>32.527253</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>9.290668999999999</v>
+        <v>6.466551</v>
       </c>
       <c r="F79" t="n">
-        <v>9.166257</v>
+        <v>6.875711</v>
       </c>
       <c r="G79" t="n">
-        <v>9.198370000000001</v>
+        <v>7.745833</v>
       </c>
       <c r="H79" t="n">
-        <v>9.698483</v>
+        <v>8.762596</v>
       </c>
       <c r="I79" t="n">
-        <v>10.265246</v>
+        <v>9.589231</v>
       </c>
       <c r="J79" t="n">
         <v>10.720745</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6.975344</v>
+        <v>6.401635</v>
       </c>
       <c r="F80" t="n">
-        <v>9.218737000000001</v>
+        <v>7.230852</v>
       </c>
       <c r="G80" t="n">
-        <v>11.600857</v>
+        <v>8.108385999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>14.311998</v>
+        <v>9.373411000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>19.500986</v>
+        <v>12.755993</v>
       </c>
       <c r="J80" t="n">
         <v>34.388148</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>12.00614</v>
+        <v>7.11686</v>
       </c>
       <c r="F81" t="n">
-        <v>10.527709</v>
+        <v>6.435672</v>
       </c>
       <c r="G81" t="n">
-        <v>9.153033000000001</v>
+        <v>6.095046</v>
       </c>
       <c r="H81" t="n">
-        <v>9.064323999999999</v>
+        <v>6.486574</v>
       </c>
       <c r="I81" t="n">
-        <v>10.276008</v>
+        <v>7.658626</v>
       </c>
       <c r="J81" t="n">
         <v>14.622391</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>13.573707</v>
+        <v>17.040642</v>
       </c>
       <c r="F82" t="n">
-        <v>16.250233</v>
+        <v>19.274649</v>
       </c>
       <c r="G82" t="n">
-        <v>18.514443</v>
+        <v>20.958813</v>
       </c>
       <c r="H82" t="n">
-        <v>18.739034</v>
+        <v>21.067967</v>
       </c>
       <c r="I82" t="n">
-        <v>17.147302</v>
+        <v>19.871777</v>
       </c>
       <c r="J82" t="n">
         <v>10.382844</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>52.530865</v>
+        <v>43.924909</v>
       </c>
       <c r="F83" t="n">
-        <v>58.030481</v>
+        <v>53.326974</v>
       </c>
       <c r="G83" t="n">
-        <v>67.54044500000001</v>
+        <v>67.271361</v>
       </c>
       <c r="H83" t="n">
-        <v>74.21799300000001</v>
+        <v>77.428972</v>
       </c>
       <c r="I83" t="n">
-        <v>73.20611700000001</v>
+        <v>79.70496900000001</v>
       </c>
       <c r="J83" t="n">
         <v>53.587295</v>
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>13.674389</v>
+        <v>13.650095</v>
       </c>
       <c r="F86" t="n">
-        <v>14.279895</v>
+        <v>14.243853</v>
       </c>
       <c r="G86" t="n">
-        <v>14.424494</v>
+        <v>14.379746</v>
       </c>
       <c r="H86" t="n">
-        <v>14.254491</v>
+        <v>14.202109</v>
       </c>
       <c r="I86" t="n">
-        <v>13.916387</v>
+        <v>13.857168</v>
       </c>
       <c r="J86" t="n">
-        <v>13.072141</v>
+        <v>13.009142</v>
       </c>
       <c r="K86" t="n">
-        <v>11.178</v>
+        <v>11.118238</v>
       </c>
       <c r="L86" t="n">
-        <v>9.168258</v>
+        <v>9.114716</v>
       </c>
       <c r="M86" t="n">
-        <v>7.917161</v>
+        <v>7.866619</v>
       </c>
       <c r="N86" t="n">
-        <v>6.802805</v>
+        <v>6.754335</v>
       </c>
       <c r="O86" t="n">
-        <v>5.609764</v>
+        <v>5.564069</v>
       </c>
       <c r="P86" t="n">
-        <v>4.632059</v>
+        <v>4.587775</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.099524</v>
+        <v>4.053897</v>
       </c>
       <c r="R86" t="n">
-        <v>3.610676</v>
+        <v>3.565064</v>
       </c>
       <c r="S86" t="n">
-        <v>3.220521</v>
+        <v>3.175448</v>
       </c>
       <c r="T86" t="n">
-        <v>2.919674</v>
+        <v>2.87476</v>
       </c>
       <c r="U86" t="n">
-        <v>2.690201</v>
+        <v>2.644309</v>
       </c>
       <c r="V86" t="n">
-        <v>2.533417</v>
+        <v>2.484323</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.866963</v>
+        <v>1.868232</v>
       </c>
       <c r="F87" t="n">
-        <v>2.18367</v>
+        <v>2.187136</v>
       </c>
       <c r="G87" t="n">
-        <v>2.516667</v>
+        <v>2.524191</v>
       </c>
       <c r="H87" t="n">
-        <v>2.773758</v>
+        <v>2.785782</v>
       </c>
       <c r="I87" t="n">
-        <v>2.951283</v>
+        <v>2.967632</v>
       </c>
       <c r="J87" t="n">
-        <v>2.970678</v>
+        <v>2.990275</v>
       </c>
       <c r="K87" t="n">
-        <v>2.689037</v>
+        <v>2.709206</v>
       </c>
       <c r="L87" t="n">
-        <v>2.314378</v>
+        <v>2.333646</v>
       </c>
       <c r="M87" t="n">
-        <v>2.083427</v>
+        <v>2.102332</v>
       </c>
       <c r="N87" t="n">
-        <v>1.857364</v>
+        <v>1.875385</v>
       </c>
       <c r="O87" t="n">
-        <v>1.583454</v>
+        <v>1.599627</v>
       </c>
       <c r="P87" t="n">
-        <v>1.346767</v>
+        <v>1.361118</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.218751</v>
+        <v>1.232278</v>
       </c>
       <c r="R87" t="n">
-        <v>1.08737</v>
+        <v>1.10003</v>
       </c>
       <c r="S87" t="n">
-        <v>0.973315</v>
+        <v>0.9853499999999999</v>
       </c>
       <c r="T87" t="n">
-        <v>0.878706</v>
+        <v>0.8903799999999999</v>
       </c>
       <c r="U87" t="n">
-        <v>0.801655</v>
+        <v>0.813259</v>
       </c>
       <c r="V87" t="n">
-        <v>0.743432</v>
+        <v>0.755401</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>29.258352</v>
+        <v>29.359207</v>
       </c>
       <c r="F88" t="n">
-        <v>27.385569</v>
+        <v>27.479207</v>
       </c>
       <c r="G88" t="n">
-        <v>25.609649</v>
+        <v>25.660528</v>
       </c>
       <c r="H88" t="n">
-        <v>24.590416</v>
+        <v>24.60677</v>
       </c>
       <c r="I88" t="n">
-        <v>24.067587</v>
+        <v>24.065254</v>
       </c>
       <c r="J88" t="n">
-        <v>23.064462</v>
+        <v>23.05687</v>
       </c>
       <c r="K88" t="n">
-        <v>20.261358</v>
+        <v>20.25514</v>
       </c>
       <c r="L88" t="n">
-        <v>17.072454</v>
+        <v>17.068598</v>
       </c>
       <c r="M88" t="n">
-        <v>15.1299</v>
+        <v>15.128324</v>
       </c>
       <c r="N88" t="n">
-        <v>13.347161</v>
+        <v>13.348497</v>
       </c>
       <c r="O88" t="n">
-        <v>11.315637</v>
+        <v>11.320306</v>
       </c>
       <c r="P88" t="n">
-        <v>9.615159</v>
+        <v>9.622522999999999</v>
       </c>
       <c r="Q88" t="n">
-        <v>8.734491</v>
+        <v>8.744225</v>
       </c>
       <c r="R88" t="n">
-        <v>7.860431</v>
+        <v>7.871901</v>
       </c>
       <c r="S88" t="n">
-        <v>7.12641</v>
+        <v>7.139301</v>
       </c>
       <c r="T88" t="n">
-        <v>6.5437</v>
+        <v>6.558435</v>
       </c>
       <c r="U88" t="n">
-        <v>6.091853</v>
+        <v>6.109131</v>
       </c>
       <c r="V88" t="n">
-        <v>5.779153</v>
+        <v>5.799942</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5.396711</v>
+        <v>5.417001</v>
       </c>
       <c r="F89" t="n">
-        <v>5.339715</v>
+        <v>5.366163</v>
       </c>
       <c r="G89" t="n">
-        <v>5.352976</v>
+        <v>5.383614</v>
       </c>
       <c r="H89" t="n">
-        <v>5.276655</v>
+        <v>5.310813</v>
       </c>
       <c r="I89" t="n">
-        <v>5.14053</v>
+        <v>5.177553</v>
       </c>
       <c r="J89" t="n">
-        <v>4.810286</v>
+        <v>4.847846</v>
       </c>
       <c r="K89" t="n">
-        <v>4.093627</v>
+        <v>4.1275</v>
       </c>
       <c r="L89" t="n">
-        <v>3.339584</v>
+        <v>3.368549</v>
       </c>
       <c r="M89" t="n">
-        <v>2.877443</v>
+        <v>2.903607</v>
       </c>
       <c r="N89" t="n">
-        <v>2.482945</v>
+        <v>2.506701</v>
       </c>
       <c r="O89" t="n">
-        <v>2.074105</v>
+        <v>2.095042</v>
       </c>
       <c r="P89" t="n">
-        <v>1.748744</v>
+        <v>1.767473</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.584422</v>
+        <v>1.602605</v>
       </c>
       <c r="R89" t="n">
-        <v>1.426265</v>
+        <v>1.44407</v>
       </c>
       <c r="S89" t="n">
-        <v>1.295838</v>
+        <v>1.313763</v>
       </c>
       <c r="T89" t="n">
-        <v>1.192851</v>
+        <v>1.211451</v>
       </c>
       <c r="U89" t="n">
-        <v>1.11227</v>
+        <v>1.132147</v>
       </c>
       <c r="V89" t="n">
-        <v>1.055043</v>
+        <v>1.077158</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>13.046718</v>
+        <v>13.020623</v>
       </c>
       <c r="F90" t="n">
-        <v>13.241602</v>
+        <v>13.187305</v>
       </c>
       <c r="G90" t="n">
-        <v>13.630413</v>
+        <v>13.565207</v>
       </c>
       <c r="H90" t="n">
-        <v>13.848743</v>
+        <v>13.781533</v>
       </c>
       <c r="I90" t="n">
-        <v>13.837734</v>
+        <v>13.771878</v>
       </c>
       <c r="J90" t="n">
-        <v>13.188657</v>
+        <v>13.126179</v>
       </c>
       <c r="K90" t="n">
-        <v>11.372738</v>
+        <v>11.318395</v>
       </c>
       <c r="L90" t="n">
-        <v>9.380855</v>
+        <v>9.335932</v>
       </c>
       <c r="M90" t="n">
-        <v>8.148286000000001</v>
+        <v>8.110049</v>
       </c>
       <c r="N90" t="n">
-        <v>7.046638</v>
+        <v>7.014473</v>
       </c>
       <c r="O90" t="n">
-        <v>5.855401</v>
+        <v>5.829198</v>
       </c>
       <c r="P90" t="n">
-        <v>4.878182</v>
+        <v>4.856407</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.350178</v>
+        <v>4.330542</v>
       </c>
       <c r="R90" t="n">
-        <v>3.850178</v>
+        <v>3.832483</v>
       </c>
       <c r="S90" t="n">
-        <v>3.440679</v>
+        <v>3.424553</v>
       </c>
       <c r="T90" t="n">
-        <v>3.118824</v>
+        <v>3.103814</v>
       </c>
       <c r="U90" t="n">
-        <v>2.869488</v>
+        <v>2.854928</v>
       </c>
       <c r="V90" t="n">
-        <v>2.695106</v>
+        <v>2.680014</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3.768224</v>
+        <v>3.753895</v>
       </c>
       <c r="F91" t="n">
-        <v>3.944339</v>
+        <v>3.921785</v>
       </c>
       <c r="G91" t="n">
-        <v>4.02572</v>
+        <v>3.998588</v>
       </c>
       <c r="H91" t="n">
-        <v>3.954439</v>
+        <v>3.922261</v>
       </c>
       <c r="I91" t="n">
-        <v>3.782275</v>
+        <v>3.744102</v>
       </c>
       <c r="J91" t="n">
-        <v>3.451631</v>
+        <v>3.40826</v>
       </c>
       <c r="K91" t="n">
-        <v>2.862355</v>
+        <v>2.818425</v>
       </c>
       <c r="L91" t="n">
-        <v>2.280519</v>
+        <v>2.239011</v>
       </c>
       <c r="M91" t="n">
-        <v>1.917424</v>
+        <v>1.877218</v>
       </c>
       <c r="N91" t="n">
-        <v>1.61363</v>
+        <v>1.576144</v>
       </c>
       <c r="O91" t="n">
-        <v>1.316276</v>
+        <v>1.28352</v>
       </c>
       <c r="P91" t="n">
-        <v>1.086113</v>
+        <v>1.05784</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.965865</v>
+        <v>0.939794</v>
       </c>
       <c r="R91" t="n">
-        <v>0.856504</v>
+        <v>0.832543</v>
       </c>
       <c r="S91" t="n">
-        <v>0.770242</v>
+        <v>0.747873</v>
       </c>
       <c r="T91" t="n">
-        <v>0.7060920000000001</v>
+        <v>0.684724</v>
       </c>
       <c r="U91" t="n">
-        <v>0.661022</v>
+        <v>0.63998</v>
       </c>
       <c r="V91" t="n">
-        <v>0.636288</v>
+        <v>0.614557</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2.131804</v>
+        <v>2.116082</v>
       </c>
       <c r="F92" t="n">
-        <v>2.255889</v>
+        <v>2.232612</v>
       </c>
       <c r="G92" t="n">
-        <v>2.369959</v>
+        <v>2.344876</v>
       </c>
       <c r="H92" t="n">
-        <v>2.387261</v>
+        <v>2.360485</v>
       </c>
       <c r="I92" t="n">
-        <v>2.334406</v>
+        <v>2.305136</v>
       </c>
       <c r="J92" t="n">
-        <v>2.174875</v>
+        <v>2.143554</v>
       </c>
       <c r="K92" t="n">
-        <v>1.835995</v>
+        <v>1.805688</v>
       </c>
       <c r="L92" t="n">
-        <v>1.482614</v>
+        <v>1.454736</v>
       </c>
       <c r="M92" t="n">
-        <v>1.263417</v>
+        <v>1.236947</v>
       </c>
       <c r="N92" t="n">
-        <v>1.076651</v>
+        <v>1.052143</v>
       </c>
       <c r="O92" t="n">
-        <v>0.886284</v>
+        <v>0.86486</v>
       </c>
       <c r="P92" t="n">
-        <v>0.735098</v>
+        <v>0.7165010000000001</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.654826</v>
+        <v>0.637637</v>
       </c>
       <c r="R92" t="n">
-        <v>0.579925</v>
+        <v>0.564165</v>
       </c>
       <c r="S92" t="n">
-        <v>0.519404</v>
+        <v>0.504738</v>
       </c>
       <c r="T92" t="n">
-        <v>0.472997</v>
+        <v>0.458974</v>
       </c>
       <c r="U92" t="n">
-        <v>0.43875</v>
+        <v>0.424856</v>
       </c>
       <c r="V92" t="n">
-        <v>0.417491</v>
+        <v>0.403066</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.457908</v>
+        <v>0.457345</v>
       </c>
       <c r="F93" t="n">
-        <v>0.503976</v>
+        <v>0.503185</v>
       </c>
       <c r="G93" t="n">
-        <v>0.558772</v>
+        <v>0.558525</v>
       </c>
       <c r="H93" t="n">
-        <v>0.6088519999999999</v>
+        <v>0.609666</v>
       </c>
       <c r="I93" t="n">
-        <v>0.646517</v>
+        <v>0.648596</v>
       </c>
       <c r="J93" t="n">
-        <v>0.646784</v>
+        <v>0.6499549999999999</v>
       </c>
       <c r="K93" t="n">
-        <v>0.577465</v>
+        <v>0.581094</v>
       </c>
       <c r="L93" t="n">
-        <v>0.487214</v>
+        <v>0.490817</v>
       </c>
       <c r="M93" t="n">
-        <v>0.428149</v>
+        <v>0.431667</v>
       </c>
       <c r="N93" t="n">
-        <v>0.37206</v>
+        <v>0.375316</v>
       </c>
       <c r="O93" t="n">
-        <v>0.30975</v>
+        <v>0.31256</v>
       </c>
       <c r="P93" t="n">
-        <v>0.258254</v>
+        <v>0.26066</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.230048</v>
+        <v>0.232261</v>
       </c>
       <c r="R93" t="n">
-        <v>0.202687</v>
+        <v>0.204723</v>
       </c>
       <c r="S93" t="n">
-        <v>0.179576</v>
+        <v>0.181479</v>
       </c>
       <c r="T93" t="n">
-        <v>0.160798</v>
+        <v>0.162611</v>
       </c>
       <c r="U93" t="n">
-        <v>0.145829</v>
+        <v>0.147591</v>
       </c>
       <c r="V93" t="n">
-        <v>0.13488</v>
+        <v>0.13666</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>82.99872999999999</v>
+        <v>83.149466</v>
       </c>
       <c r="F94" t="n">
-        <v>91.25282900000001</v>
+        <v>91.537251</v>
       </c>
       <c r="G94" t="n">
-        <v>95.134764</v>
+        <v>95.511537</v>
       </c>
       <c r="H94" t="n">
-        <v>95.102434</v>
+        <v>95.539627</v>
       </c>
       <c r="I94" t="n">
-        <v>92.50463999999999</v>
+        <v>92.974817</v>
       </c>
       <c r="J94" t="n">
-        <v>85.974609</v>
+        <v>86.445505</v>
       </c>
       <c r="K94" t="n">
-        <v>72.622805</v>
+        <v>73.045222</v>
       </c>
       <c r="L94" t="n">
-        <v>58.821553</v>
+        <v>59.182338</v>
       </c>
       <c r="M94" t="n">
-        <v>50.147345</v>
+        <v>50.468191</v>
       </c>
       <c r="N94" t="n">
-        <v>42.570356</v>
+        <v>42.85135</v>
       </c>
       <c r="O94" t="n">
-        <v>34.781898</v>
+        <v>35.016897</v>
       </c>
       <c r="P94" t="n">
-        <v>28.536246</v>
+        <v>28.734011</v>
       </c>
       <c r="Q94" t="n">
-        <v>25.06341</v>
+        <v>25.24227</v>
       </c>
       <c r="R94" t="n">
-        <v>21.82086</v>
+        <v>21.981367</v>
       </c>
       <c r="S94" t="n">
-        <v>19.160934</v>
+        <v>19.306248</v>
       </c>
       <c r="T94" t="n">
-        <v>17.0685</v>
+        <v>17.202375</v>
       </c>
       <c r="U94" t="n">
-        <v>15.461461</v>
+        <v>15.588617</v>
       </c>
       <c r="V94" t="n">
-        <v>14.326432</v>
+        <v>14.453314</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>22.523804</v>
+        <v>22.310903</v>
       </c>
       <c r="F95" t="n">
-        <v>25.391019</v>
+        <v>25.116797</v>
       </c>
       <c r="G95" t="n">
-        <v>27.498773</v>
+        <v>27.22737</v>
       </c>
       <c r="H95" t="n">
-        <v>28.500656</v>
+        <v>28.241838</v>
       </c>
       <c r="I95" t="n">
-        <v>28.661825</v>
+        <v>28.416023</v>
       </c>
       <c r="J95" t="n">
-        <v>27.276011</v>
+        <v>27.047245</v>
       </c>
       <c r="K95" t="n">
-        <v>23.342749</v>
+        <v>23.147252</v>
       </c>
       <c r="L95" t="n">
-        <v>18.982849</v>
+        <v>18.82199</v>
       </c>
       <c r="M95" t="n">
-        <v>16.165062</v>
+        <v>16.026698</v>
       </c>
       <c r="N95" t="n">
-        <v>13.658358</v>
+        <v>13.540888</v>
       </c>
       <c r="O95" t="n">
-        <v>11.086205</v>
+        <v>10.990556</v>
       </c>
       <c r="P95" t="n">
-        <v>9.036549000000001</v>
+        <v>8.958406</v>
       </c>
       <c r="Q95" t="n">
-        <v>7.899166</v>
+        <v>7.830579</v>
       </c>
       <c r="R95" t="n">
-        <v>6.867003</v>
+        <v>6.807103</v>
       </c>
       <c r="S95" t="n">
-        <v>6.04261</v>
+        <v>5.98957</v>
       </c>
       <c r="T95" t="n">
-        <v>5.410769</v>
+        <v>5.362657</v>
       </c>
       <c r="U95" t="n">
-        <v>4.932835</v>
+        <v>4.887567</v>
       </c>
       <c r="V95" t="n">
-        <v>4.605417</v>
+        <v>4.560745</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>9.383464</v>
+        <v>9.395315</v>
       </c>
       <c r="F96" t="n">
-        <v>9.217629000000001</v>
+        <v>9.21871</v>
       </c>
       <c r="G96" t="n">
-        <v>8.715992</v>
+        <v>8.693111</v>
       </c>
       <c r="H96" t="n">
-        <v>8.331215</v>
+        <v>8.286505999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>8.057344000000001</v>
+        <v>7.997119</v>
       </c>
       <c r="J96" t="n">
-        <v>7.607407</v>
+        <v>7.540365</v>
       </c>
       <c r="K96" t="n">
-        <v>6.577478</v>
+        <v>6.513994</v>
       </c>
       <c r="L96" t="n">
-        <v>5.459292</v>
+        <v>5.403206</v>
       </c>
       <c r="M96" t="n">
-        <v>4.765812</v>
+        <v>4.71432</v>
       </c>
       <c r="N96" t="n">
-        <v>4.139023</v>
+        <v>4.092646</v>
       </c>
       <c r="O96" t="n">
-        <v>3.454777</v>
+        <v>3.415304</v>
       </c>
       <c r="P96" t="n">
-        <v>2.892879</v>
+        <v>2.859508</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.593593</v>
+        <v>2.563397</v>
       </c>
       <c r="R96" t="n">
-        <v>2.306845</v>
+        <v>2.279483</v>
       </c>
       <c r="S96" t="n">
-        <v>2.070357</v>
+        <v>2.044939</v>
       </c>
       <c r="T96" t="n">
-        <v>1.884455</v>
+        <v>1.860072</v>
       </c>
       <c r="U96" t="n">
-        <v>1.742595</v>
+        <v>1.718406</v>
       </c>
       <c r="V96" t="n">
-        <v>1.648101</v>
+        <v>1.623012</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3.876316</v>
+        <v>3.885221</v>
       </c>
       <c r="F97" t="n">
-        <v>3.522868</v>
+        <v>3.524998</v>
       </c>
       <c r="G97" t="n">
-        <v>3.239068</v>
+        <v>3.229954</v>
       </c>
       <c r="H97" t="n">
-        <v>3.087912</v>
+        <v>3.06944</v>
       </c>
       <c r="I97" t="n">
-        <v>3.021382</v>
+        <v>2.996635</v>
       </c>
       <c r="J97" t="n">
-        <v>2.897918</v>
+        <v>2.870264</v>
       </c>
       <c r="K97" t="n">
-        <v>2.544247</v>
+        <v>2.5177</v>
       </c>
       <c r="L97" t="n">
-        <v>2.140831</v>
+        <v>2.116861</v>
       </c>
       <c r="M97" t="n">
-        <v>1.895092</v>
+        <v>1.872547</v>
       </c>
       <c r="N97" t="n">
-        <v>1.67229</v>
+        <v>1.651401</v>
       </c>
       <c r="O97" t="n">
-        <v>1.422297</v>
+        <v>1.40391</v>
       </c>
       <c r="P97" t="n">
-        <v>1.216904</v>
+        <v>1.200734</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.116383</v>
+        <v>1.101172</v>
       </c>
       <c r="R97" t="n">
-        <v>1.016149</v>
+        <v>1.001959</v>
       </c>
       <c r="S97" t="n">
-        <v>0.9322859999999999</v>
+        <v>0.91891</v>
       </c>
       <c r="T97" t="n">
-        <v>0.865765</v>
+        <v>0.852878</v>
       </c>
       <c r="U97" t="n">
-        <v>0.8147799999999999</v>
+        <v>0.801946</v>
       </c>
       <c r="V97" t="n">
-        <v>0.782338</v>
+        <v>0.768907</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>17.968644</v>
+        <v>18.014742</v>
       </c>
       <c r="F98" t="n">
-        <v>16.857001</v>
+        <v>16.88557</v>
       </c>
       <c r="G98" t="n">
-        <v>16.0274</v>
+        <v>16.017182</v>
       </c>
       <c r="H98" t="n">
-        <v>15.290764</v>
+        <v>15.247784</v>
       </c>
       <c r="I98" t="n">
-        <v>14.731515</v>
+        <v>14.665517</v>
       </c>
       <c r="J98" t="n">
-        <v>13.814453</v>
+        <v>13.736698</v>
       </c>
       <c r="K98" t="n">
-        <v>11.770282</v>
+        <v>11.694887</v>
       </c>
       <c r="L98" t="n">
-        <v>9.605612000000001</v>
+        <v>9.539203000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>8.206289</v>
+        <v>8.14677</v>
       </c>
       <c r="N98" t="n">
-        <v>7.117953</v>
+        <v>7.064704</v>
       </c>
       <c r="O98" t="n">
-        <v>6.144314</v>
+        <v>6.097417</v>
       </c>
       <c r="P98" t="n">
-        <v>5.536665</v>
+        <v>5.493826</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.389314</v>
+        <v>5.347235</v>
       </c>
       <c r="R98" t="n">
-        <v>5.330768</v>
+        <v>5.288974</v>
       </c>
       <c r="S98" t="n">
-        <v>5.257523</v>
+        <v>5.216339</v>
       </c>
       <c r="T98" t="n">
-        <v>5.190015</v>
+        <v>5.149563</v>
       </c>
       <c r="U98" t="n">
-        <v>5.156975</v>
+        <v>5.117407</v>
       </c>
       <c r="V98" t="n">
-        <v>5.145964</v>
+        <v>5.107798</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26.621986</v>
+        <v>26.716686</v>
       </c>
       <c r="F99" t="n">
-        <v>26.352528</v>
+        <v>26.505771</v>
       </c>
       <c r="G99" t="n">
-        <v>25.971857</v>
+        <v>26.161416</v>
       </c>
       <c r="H99" t="n">
-        <v>25.153484</v>
+        <v>25.358957</v>
       </c>
       <c r="I99" t="n">
-        <v>24.31392</v>
+        <v>24.523384</v>
       </c>
       <c r="J99" t="n">
-        <v>22.721812</v>
+        <v>22.921917</v>
       </c>
       <c r="K99" t="n">
-        <v>19.20738</v>
+        <v>19.377455</v>
       </c>
       <c r="L99" t="n">
-        <v>15.526989</v>
+        <v>15.664164</v>
       </c>
       <c r="M99" t="n">
-        <v>13.150374</v>
+        <v>13.265899</v>
       </c>
       <c r="N99" t="n">
-        <v>11.327811</v>
+        <v>11.426761</v>
       </c>
       <c r="O99" t="n">
-        <v>9.731033</v>
+        <v>9.815666999999999</v>
       </c>
       <c r="P99" t="n">
-        <v>8.721859</v>
+        <v>8.797625</v>
       </c>
       <c r="Q99" t="n">
-        <v>8.426920000000001</v>
+        <v>8.500264</v>
       </c>
       <c r="R99" t="n">
-        <v>8.253843</v>
+        <v>8.32597</v>
       </c>
       <c r="S99" t="n">
-        <v>8.032614000000001</v>
+        <v>8.103248000000001</v>
       </c>
       <c r="T99" t="n">
-        <v>7.779621</v>
+        <v>7.848549</v>
       </c>
       <c r="U99" t="n">
-        <v>7.525676</v>
+        <v>7.592925</v>
       </c>
       <c r="V99" t="n">
-        <v>7.223026</v>
+        <v>7.287986</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>9.939544</v>
+        <v>9.932202</v>
       </c>
       <c r="F100" t="n">
-        <v>9.946605999999999</v>
+        <v>9.914042</v>
       </c>
       <c r="G100" t="n">
-        <v>9.96983</v>
+        <v>9.910907999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>9.877230000000001</v>
+        <v>9.798761000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>9.782628000000001</v>
+        <v>9.690863999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>9.373063999999999</v>
+        <v>9.276204</v>
       </c>
       <c r="K100" t="n">
-        <v>8.136298</v>
+        <v>8.047200999999999</v>
       </c>
       <c r="L100" t="n">
-        <v>6.771887</v>
+        <v>6.694974</v>
       </c>
       <c r="M100" t="n">
-        <v>5.918152</v>
+        <v>5.849283</v>
       </c>
       <c r="N100" t="n">
-        <v>5.265332</v>
+        <v>5.203095</v>
       </c>
       <c r="O100" t="n">
-        <v>4.672978</v>
+        <v>4.61726</v>
       </c>
       <c r="P100" t="n">
-        <v>4.330914</v>
+        <v>4.279205</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.335036</v>
+        <v>4.283545</v>
       </c>
       <c r="R100" t="n">
-        <v>4.413368</v>
+        <v>4.361465</v>
       </c>
       <c r="S100" t="n">
-        <v>4.487299</v>
+        <v>4.435287</v>
       </c>
       <c r="T100" t="n">
-        <v>4.574609</v>
+        <v>4.522648</v>
       </c>
       <c r="U100" t="n">
-        <v>4.709358</v>
+        <v>4.657455</v>
       </c>
       <c r="V100" t="n">
-        <v>4.893583</v>
+        <v>4.842117</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>12.484181</v>
+        <v>12.507614</v>
       </c>
       <c r="F101" t="n">
-        <v>12.137779</v>
+        <v>12.161939</v>
       </c>
       <c r="G101" t="n">
-        <v>11.713313</v>
+        <v>11.730448</v>
       </c>
       <c r="H101" t="n">
-        <v>11.160023</v>
+        <v>11.169219</v>
       </c>
       <c r="I101" t="n">
-        <v>10.675729</v>
+        <v>10.677819</v>
       </c>
       <c r="J101" t="n">
-        <v>9.939989000000001</v>
+        <v>9.936432999999999</v>
       </c>
       <c r="K101" t="n">
-        <v>8.432043999999999</v>
+        <v>8.424892</v>
       </c>
       <c r="L101" t="n">
-        <v>6.885437</v>
+        <v>6.876566</v>
       </c>
       <c r="M101" t="n">
-        <v>5.919646</v>
+        <v>5.909679</v>
       </c>
       <c r="N101" t="n">
-        <v>5.190813</v>
+        <v>5.180417</v>
       </c>
       <c r="O101" t="n">
-        <v>4.547327</v>
+        <v>4.537145</v>
       </c>
       <c r="P101" t="n">
-        <v>4.162936</v>
+        <v>4.152967</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.116424</v>
+        <v>4.106129</v>
       </c>
       <c r="R101" t="n">
-        <v>4.136455</v>
+        <v>4.125746</v>
       </c>
       <c r="S101" t="n">
-        <v>4.145567</v>
+        <v>4.134438</v>
       </c>
       <c r="T101" t="n">
-        <v>4.156298</v>
+        <v>4.144724</v>
       </c>
       <c r="U101" t="n">
-        <v>4.190732</v>
+        <v>4.17878</v>
       </c>
       <c r="V101" t="n">
-        <v>4.236012</v>
+        <v>4.223864</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>101.357328</v>
+        <v>101.133428</v>
       </c>
       <c r="F102" t="n">
-        <v>105.37959</v>
+        <v>105.174825</v>
       </c>
       <c r="G102" t="n">
-        <v>104.73011</v>
+        <v>104.614435</v>
       </c>
       <c r="H102" t="n">
-        <v>101.56574</v>
+        <v>101.530002</v>
       </c>
       <c r="I102" t="n">
-        <v>98.565288</v>
+        <v>98.58356499999999</v>
       </c>
       <c r="J102" t="n">
-        <v>92.844999</v>
+        <v>92.893308</v>
       </c>
       <c r="K102" t="n">
-        <v>79.33167299999999</v>
+        <v>79.387389</v>
       </c>
       <c r="L102" t="n">
-        <v>64.926579</v>
+        <v>64.977465</v>
       </c>
       <c r="M102" t="n">
-        <v>55.727049</v>
+        <v>55.770663</v>
       </c>
       <c r="N102" t="n">
-        <v>48.683239</v>
+        <v>48.71867</v>
       </c>
       <c r="O102" t="n">
-        <v>42.457984</v>
+        <v>42.48517</v>
       </c>
       <c r="P102" t="n">
-        <v>38.690057</v>
+        <v>38.711475</v>
       </c>
       <c r="Q102" t="n">
-        <v>38.066762</v>
+        <v>38.08499</v>
       </c>
       <c r="R102" t="n">
-        <v>38.033708</v>
+        <v>38.049314</v>
       </c>
       <c r="S102" t="n">
-        <v>37.841682</v>
+        <v>37.854946</v>
       </c>
       <c r="T102" t="n">
-        <v>37.528973</v>
+        <v>37.540531</v>
       </c>
       <c r="U102" t="n">
-        <v>37.336026</v>
+        <v>37.34555</v>
       </c>
       <c r="V102" t="n">
-        <v>37.192075</v>
+        <v>37.198529</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>211.072968</v>
+        <v>211.552946</v>
       </c>
       <c r="F103" t="n">
-        <v>194.322857</v>
+        <v>194.483323</v>
       </c>
       <c r="G103" t="n">
-        <v>182.846525</v>
+        <v>182.499659</v>
       </c>
       <c r="H103" t="n">
-        <v>172.838942</v>
+        <v>172.111489</v>
       </c>
       <c r="I103" t="n">
-        <v>164.731202</v>
+        <v>163.774274</v>
       </c>
       <c r="J103" t="n">
-        <v>152.468478</v>
+        <v>151.433975</v>
       </c>
       <c r="K103" t="n">
-        <v>127.882799</v>
+        <v>126.948671</v>
       </c>
       <c r="L103" t="n">
-        <v>102.624709</v>
+        <v>101.851768</v>
       </c>
       <c r="M103" t="n">
-        <v>86.26531</v>
+        <v>85.609708</v>
       </c>
       <c r="N103" t="n">
-        <v>73.803839</v>
+        <v>73.24332800000001</v>
       </c>
       <c r="O103" t="n">
-        <v>63.016591</v>
+        <v>62.541657</v>
       </c>
       <c r="P103" t="n">
-        <v>56.277419</v>
+        <v>55.859169</v>
       </c>
       <c r="Q103" t="n">
-        <v>54.318986</v>
+        <v>53.9237</v>
       </c>
       <c r="R103" t="n">
-        <v>53.27314</v>
+        <v>52.896352</v>
       </c>
       <c r="S103" t="n">
-        <v>52.092795</v>
+        <v>51.736124</v>
       </c>
       <c r="T103" t="n">
-        <v>50.998686</v>
+        <v>50.660896</v>
       </c>
       <c r="U103" t="n">
-        <v>50.321086</v>
+        <v>49.999936</v>
       </c>
       <c r="V103" t="n">
-        <v>49.757508</v>
+        <v>49.45753</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>21.028138</v>
+        <v>20.98546</v>
       </c>
       <c r="F104" t="n">
-        <v>21.146236</v>
+        <v>21.106691</v>
       </c>
       <c r="G104" t="n">
-        <v>20.36762</v>
+        <v>20.340991</v>
       </c>
       <c r="H104" t="n">
-        <v>19.207186</v>
+        <v>19.198956</v>
       </c>
       <c r="I104" t="n">
-        <v>18.185673</v>
+        <v>18.193211</v>
       </c>
       <c r="J104" t="n">
-        <v>16.754306</v>
+        <v>16.773113</v>
       </c>
       <c r="K104" t="n">
-        <v>14.015093</v>
+        <v>14.038416</v>
       </c>
       <c r="L104" t="n">
-        <v>11.216603</v>
+        <v>11.239682</v>
       </c>
       <c r="M104" t="n">
-        <v>9.394942</v>
+        <v>9.416793999999999</v>
       </c>
       <c r="N104" t="n">
-        <v>7.994054</v>
+        <v>8.013975</v>
       </c>
       <c r="O104" t="n">
-        <v>6.774353</v>
+        <v>6.791808</v>
       </c>
       <c r="P104" t="n">
-        <v>5.988175</v>
+        <v>6.003708</v>
       </c>
       <c r="Q104" t="n">
-        <v>5.710208</v>
+        <v>5.724776</v>
       </c>
       <c r="R104" t="n">
-        <v>5.531277</v>
+        <v>5.544896</v>
       </c>
       <c r="S104" t="n">
-        <v>5.341119</v>
+        <v>5.35366</v>
       </c>
       <c r="T104" t="n">
-        <v>5.156752</v>
+        <v>5.168217</v>
       </c>
       <c r="U104" t="n">
-        <v>4.999275</v>
+        <v>5.009831</v>
       </c>
       <c r="V104" t="n">
-        <v>4.841122</v>
+        <v>4.850825</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>10.236086</v>
+        <v>10.254808</v>
       </c>
       <c r="F105" t="n">
-        <v>10.279197</v>
+        <v>10.298338</v>
       </c>
       <c r="G105" t="n">
-        <v>10.241837</v>
+        <v>10.260648</v>
       </c>
       <c r="H105" t="n">
-        <v>10.018337</v>
+        <v>10.035326</v>
       </c>
       <c r="I105" t="n">
-        <v>9.818749</v>
+        <v>9.832312</v>
       </c>
       <c r="J105" t="n">
-        <v>9.350866999999999</v>
+        <v>9.359055</v>
       </c>
       <c r="K105" t="n">
-        <v>8.090386000000001</v>
+        <v>8.092815</v>
       </c>
       <c r="L105" t="n">
-        <v>6.705101</v>
+        <v>6.703554</v>
       </c>
       <c r="M105" t="n">
-        <v>5.818153</v>
+        <v>5.814342</v>
       </c>
       <c r="N105" t="n">
-        <v>5.12635</v>
+        <v>5.121273</v>
       </c>
       <c r="O105" t="n">
-        <v>4.497823</v>
+        <v>4.492028</v>
       </c>
       <c r="P105" t="n">
-        <v>4.117922</v>
+        <v>4.111377</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.069642</v>
+        <v>4.061907</v>
       </c>
       <c r="R105" t="n">
-        <v>4.086977</v>
+        <v>4.07795</v>
       </c>
       <c r="S105" t="n">
-        <v>4.092059</v>
+        <v>4.081896</v>
       </c>
       <c r="T105" t="n">
-        <v>4.096459</v>
+        <v>4.085357</v>
       </c>
       <c r="U105" t="n">
-        <v>4.124073</v>
+        <v>4.11221</v>
       </c>
       <c r="V105" t="n">
-        <v>4.167368</v>
+        <v>4.154867</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>109.059925</v>
+        <v>108.775199</v>
       </c>
       <c r="F106" t="n">
-        <v>111.44253</v>
+        <v>111.272922</v>
       </c>
       <c r="G106" t="n">
-        <v>108.478602</v>
+        <v>108.5267</v>
       </c>
       <c r="H106" t="n">
-        <v>103.240089</v>
+        <v>103.442719</v>
       </c>
       <c r="I106" t="n">
-        <v>98.356657</v>
+        <v>98.646744</v>
       </c>
       <c r="J106" t="n">
-        <v>90.82685499999999</v>
+        <v>91.147238</v>
       </c>
       <c r="K106" t="n">
-        <v>75.91382400000001</v>
+        <v>76.205074</v>
       </c>
       <c r="L106" t="n">
-        <v>60.611705</v>
+        <v>60.852213</v>
       </c>
       <c r="M106" t="n">
-        <v>50.62053</v>
+        <v>50.823342</v>
       </c>
       <c r="N106" t="n">
-        <v>42.937238</v>
+        <v>43.108725</v>
       </c>
       <c r="O106" t="n">
-        <v>36.288692</v>
+        <v>36.431808</v>
       </c>
       <c r="P106" t="n">
-        <v>32.013465</v>
+        <v>32.137057</v>
       </c>
       <c r="Q106" t="n">
-        <v>30.500319</v>
+        <v>30.614696</v>
       </c>
       <c r="R106" t="n">
-        <v>29.548235</v>
+        <v>29.655232</v>
       </c>
       <c r="S106" t="n">
-        <v>28.55172</v>
+        <v>28.651676</v>
       </c>
       <c r="T106" t="n">
-        <v>27.532461</v>
+        <v>27.62671</v>
       </c>
       <c r="U106" t="n">
-        <v>26.585676</v>
+        <v>26.675561</v>
       </c>
       <c r="V106" t="n">
-        <v>25.628116</v>
+        <v>25.712609</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2.130303</v>
+        <v>2.149371</v>
       </c>
       <c r="F107" t="n">
-        <v>2.088127</v>
+        <v>2.11521</v>
       </c>
       <c r="G107" t="n">
-        <v>2.025252</v>
+        <v>2.054419</v>
       </c>
       <c r="H107" t="n">
-        <v>1.95527</v>
+        <v>1.984501</v>
       </c>
       <c r="I107" t="n">
-        <v>1.9107</v>
+        <v>1.939749</v>
       </c>
       <c r="J107" t="n">
-        <v>1.82405</v>
+        <v>1.852146</v>
       </c>
       <c r="K107" t="n">
-        <v>1.583441</v>
+        <v>1.608169</v>
       </c>
       <c r="L107" t="n">
-        <v>1.314998</v>
+        <v>1.335861</v>
       </c>
       <c r="M107" t="n">
-        <v>1.140473</v>
+        <v>1.158872</v>
       </c>
       <c r="N107" t="n">
-        <v>1.00077</v>
+        <v>1.0172</v>
       </c>
       <c r="O107" t="n">
-        <v>0.870471</v>
+        <v>0.885026</v>
       </c>
       <c r="P107" t="n">
-        <v>0.78445</v>
+        <v>0.797849</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.756419</v>
+        <v>0.769664</v>
       </c>
       <c r="R107" t="n">
-        <v>0.734069</v>
+        <v>0.747287</v>
       </c>
       <c r="S107" t="n">
-        <v>0.702524</v>
+        <v>0.71558</v>
       </c>
       <c r="T107" t="n">
-        <v>0.6635529999999999</v>
+        <v>0.676337</v>
       </c>
       <c r="U107" t="n">
-        <v>0.619846</v>
+        <v>0.632302</v>
       </c>
       <c r="V107" t="n">
-        <v>0.567124</v>
+        <v>0.579094</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>42.571597</v>
+        <v>42.781689</v>
       </c>
       <c r="F108" t="n">
-        <v>39.961884</v>
+        <v>40.229047</v>
       </c>
       <c r="G108" t="n">
-        <v>37.639952</v>
+        <v>37.899556</v>
       </c>
       <c r="H108" t="n">
-        <v>35.294772</v>
+        <v>35.531209</v>
       </c>
       <c r="I108" t="n">
-        <v>33.352997</v>
+        <v>33.56679</v>
       </c>
       <c r="J108" t="n">
-        <v>30.71101</v>
+        <v>30.900706</v>
       </c>
       <c r="K108" t="n">
-        <v>25.727633</v>
+        <v>25.88233</v>
       </c>
       <c r="L108" t="n">
-        <v>20.701881</v>
+        <v>20.824284</v>
       </c>
       <c r="M108" t="n">
-        <v>17.504731</v>
+        <v>17.60691</v>
       </c>
       <c r="N108" t="n">
-        <v>15.084704</v>
+        <v>15.171826</v>
       </c>
       <c r="O108" t="n">
-        <v>12.990024</v>
+        <v>13.064345</v>
       </c>
       <c r="P108" t="n">
-        <v>11.692253</v>
+        <v>11.758946</v>
       </c>
       <c r="Q108" t="n">
-        <v>11.362532</v>
+        <v>11.427587</v>
       </c>
       <c r="R108" t="n">
-        <v>11.206916</v>
+        <v>11.27161</v>
       </c>
       <c r="S108" t="n">
-        <v>10.994508</v>
+        <v>11.058604</v>
       </c>
       <c r="T108" t="n">
-        <v>10.747928</v>
+        <v>10.810959</v>
       </c>
       <c r="U108" t="n">
-        <v>10.518276</v>
+        <v>10.579822</v>
       </c>
       <c r="V108" t="n">
-        <v>10.246535</v>
+        <v>10.305808</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>20.253064</v>
+        <v>20.057528</v>
       </c>
       <c r="F109" t="n">
-        <v>22.297578</v>
+        <v>22.062636</v>
       </c>
       <c r="G109" t="n">
-        <v>21.847038</v>
+        <v>21.648945</v>
       </c>
       <c r="H109" t="n">
-        <v>20.464759</v>
+        <v>20.324257</v>
       </c>
       <c r="I109" t="n">
-        <v>19.232133</v>
+        <v>19.144038</v>
       </c>
       <c r="J109" t="n">
-        <v>17.702013</v>
+        <v>17.653817</v>
       </c>
       <c r="K109" t="n">
-        <v>14.869051</v>
+        <v>14.848689</v>
       </c>
       <c r="L109" t="n">
-        <v>11.992828</v>
+        <v>11.987474</v>
       </c>
       <c r="M109" t="n">
-        <v>10.139086</v>
+        <v>10.140717</v>
       </c>
       <c r="N109" t="n">
-        <v>8.71204</v>
+        <v>8.716917</v>
       </c>
       <c r="O109" t="n">
-        <v>7.456318</v>
+        <v>7.462455</v>
       </c>
       <c r="P109" t="n">
-        <v>6.654793</v>
+        <v>6.661429</v>
       </c>
       <c r="Q109" t="n">
-        <v>6.404402</v>
+        <v>6.411446</v>
       </c>
       <c r="R109" t="n">
-        <v>6.25906</v>
+        <v>6.266147</v>
       </c>
       <c r="S109" t="n">
-        <v>6.09736</v>
+        <v>6.104169</v>
       </c>
       <c r="T109" t="n">
-        <v>5.936383</v>
+        <v>5.942784</v>
       </c>
       <c r="U109" t="n">
-        <v>5.804168</v>
+        <v>5.810208</v>
       </c>
       <c r="V109" t="n">
-        <v>5.672282</v>
+        <v>5.677944</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>12.871238</v>
+        <v>12.849125</v>
       </c>
       <c r="F110" t="n">
-        <v>13.490327</v>
+        <v>13.474247</v>
       </c>
       <c r="G110" t="n">
-        <v>13.559478</v>
+        <v>13.555883</v>
       </c>
       <c r="H110" t="n">
-        <v>13.260432</v>
+        <v>13.26463</v>
       </c>
       <c r="I110" t="n">
-        <v>12.94324</v>
+        <v>12.949323</v>
       </c>
       <c r="J110" t="n">
-        <v>12.28333</v>
+        <v>12.287151</v>
       </c>
       <c r="K110" t="n">
-        <v>10.621746</v>
+        <v>10.621142</v>
       </c>
       <c r="L110" t="n">
-        <v>8.836076</v>
+        <v>8.831571</v>
       </c>
       <c r="M110" t="n">
-        <v>7.723729</v>
+        <v>7.716431</v>
       </c>
       <c r="N110" t="n">
-        <v>6.868322</v>
+        <v>6.859444</v>
       </c>
       <c r="O110" t="n">
-        <v>6.083507</v>
+        <v>6.074054</v>
       </c>
       <c r="P110" t="n">
-        <v>5.623499</v>
+        <v>5.613516</v>
       </c>
       <c r="Q110" t="n">
-        <v>5.612932</v>
+        <v>5.601709</v>
       </c>
       <c r="R110" t="n">
-        <v>5.691809</v>
+        <v>5.679084</v>
       </c>
       <c r="S110" t="n">
-        <v>5.748241</v>
+        <v>5.734114</v>
       </c>
       <c r="T110" t="n">
-        <v>5.795988</v>
+        <v>5.780638</v>
       </c>
       <c r="U110" t="n">
-        <v>5.870389</v>
+        <v>5.853945</v>
       </c>
       <c r="V110" t="n">
-        <v>5.957736</v>
+        <v>5.940426</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>84.120386</v>
+        <v>83.921496</v>
       </c>
       <c r="F111" t="n">
-        <v>86.80628900000001</v>
+        <v>86.627036</v>
       </c>
       <c r="G111" t="n">
-        <v>85.167846</v>
+        <v>85.04047</v>
       </c>
       <c r="H111" t="n">
-        <v>81.49491</v>
+        <v>81.40783</v>
       </c>
       <c r="I111" t="n">
-        <v>78.223249</v>
+        <v>78.16288900000001</v>
       </c>
       <c r="J111" t="n">
-        <v>73.089263</v>
+        <v>73.045416</v>
       </c>
       <c r="K111" t="n">
-        <v>62.006718</v>
+        <v>61.97407</v>
       </c>
       <c r="L111" t="n">
-        <v>50.314898</v>
+        <v>50.289338</v>
       </c>
       <c r="M111" t="n">
-        <v>42.679946</v>
+        <v>42.659606</v>
       </c>
       <c r="N111" t="n">
-        <v>36.72333</v>
+        <v>36.707255</v>
       </c>
       <c r="O111" t="n">
-        <v>31.44996</v>
+        <v>31.43623</v>
       </c>
       <c r="P111" t="n">
-        <v>28.112928</v>
+        <v>28.098202</v>
       </c>
       <c r="Q111" t="n">
-        <v>27.143926</v>
+        <v>27.124695</v>
       </c>
       <c r="R111" t="n">
-        <v>26.651578</v>
+        <v>26.625919</v>
       </c>
       <c r="S111" t="n">
-        <v>26.121</v>
+        <v>26.088545</v>
       </c>
       <c r="T111" t="n">
-        <v>25.592335</v>
+        <v>25.554552</v>
       </c>
       <c r="U111" t="n">
-        <v>25.180216</v>
+        <v>25.139148</v>
       </c>
       <c r="V111" t="n">
-        <v>24.838783</v>
+        <v>24.795181</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>116.512082</v>
+        <v>116.595177</v>
       </c>
       <c r="F112" t="n">
-        <v>117.916376</v>
+        <v>118.113308</v>
       </c>
       <c r="G112" t="n">
-        <v>116.867966</v>
+        <v>117.192966</v>
       </c>
       <c r="H112" t="n">
-        <v>113.585175</v>
+        <v>114.001473</v>
       </c>
       <c r="I112" t="n">
-        <v>110.465492</v>
+        <v>110.938694</v>
       </c>
       <c r="J112" t="n">
-        <v>104.199143</v>
+        <v>104.686456</v>
       </c>
       <c r="K112" t="n">
-        <v>89.174651</v>
+        <v>89.611819</v>
       </c>
       <c r="L112" t="n">
-        <v>73.07930899999999</v>
+        <v>73.446495</v>
       </c>
       <c r="M112" t="n">
-        <v>62.745692</v>
+        <v>63.065086</v>
       </c>
       <c r="N112" t="n">
-        <v>54.761886</v>
+        <v>55.044091</v>
       </c>
       <c r="O112" t="n">
-        <v>47.653025</v>
+        <v>47.902328</v>
       </c>
       <c r="P112" t="n">
-        <v>43.274666</v>
+        <v>43.505651</v>
       </c>
       <c r="Q112" t="n">
-        <v>42.381018</v>
+        <v>42.612497</v>
       </c>
       <c r="R112" t="n">
-        <v>42.091534</v>
+        <v>42.326793</v>
       </c>
       <c r="S112" t="n">
-        <v>41.554684</v>
+        <v>41.792071</v>
       </c>
       <c r="T112" t="n">
-        <v>40.86744</v>
+        <v>41.105035</v>
       </c>
       <c r="U112" t="n">
-        <v>40.229153</v>
+        <v>40.465845</v>
       </c>
       <c r="V112" t="n">
-        <v>39.462596</v>
+        <v>39.69525</v>
       </c>
     </row>
     <row r="113">
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>15.661845</v>
+        <v>15.671592</v>
       </c>
       <c r="F113" t="n">
-        <v>16.19593</v>
+        <v>16.205909</v>
       </c>
       <c r="G113" t="n">
-        <v>14.562503</v>
+        <v>14.563964</v>
       </c>
       <c r="H113" t="n">
-        <v>13.47634</v>
+        <v>13.46616</v>
       </c>
       <c r="I113" t="n">
-        <v>13.000764</v>
+        <v>12.96469</v>
       </c>
       <c r="J113" t="n">
         <v>16.718039</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2.215424</v>
+        <v>2.207989</v>
       </c>
       <c r="F114" t="n">
-        <v>3.240846</v>
+        <v>3.232536</v>
       </c>
       <c r="G114" t="n">
-        <v>4.353578</v>
+        <v>4.347641</v>
       </c>
       <c r="H114" t="n">
-        <v>5.283771</v>
+        <v>5.279903</v>
       </c>
       <c r="I114" t="n">
-        <v>5.84565</v>
+        <v>5.843665</v>
       </c>
       <c r="J114" t="n">
         <v>5.024452</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>59.920287</v>
+        <v>59.917976</v>
       </c>
       <c r="F115" t="n">
-        <v>71.235467</v>
+        <v>71.23379799999999</v>
       </c>
       <c r="G115" t="n">
-        <v>80.095534</v>
+        <v>80.10001</v>
       </c>
       <c r="H115" t="n">
-        <v>87.58541</v>
+        <v>87.599457</v>
       </c>
       <c r="I115" t="n">
-        <v>93.228539</v>
+        <v>93.266598</v>
       </c>
       <c r="J115" t="n">
         <v>77.352782</v>
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1.526927</v>
+        <v>1.523021</v>
       </c>
       <c r="F116" t="n">
-        <v>1.655355</v>
+        <v>1.648364</v>
       </c>
       <c r="G116" t="n">
-        <v>1.772895</v>
+        <v>1.76358</v>
       </c>
       <c r="H116" t="n">
-        <v>1.837408</v>
+        <v>1.826342</v>
       </c>
       <c r="I116" t="n">
-        <v>1.862411</v>
+        <v>1.850012</v>
       </c>
       <c r="J116" t="n">
-        <v>1.693769</v>
+        <v>1.681541</v>
       </c>
       <c r="K116" t="n">
-        <v>1.487202</v>
+        <v>1.475717</v>
       </c>
       <c r="L116" t="n">
-        <v>1.267596</v>
+        <v>1.257201</v>
       </c>
       <c r="M116" t="n">
-        <v>1.122977</v>
+        <v>1.113262</v>
       </c>
       <c r="N116" t="n">
-        <v>0.996324</v>
+        <v>0.98748</v>
       </c>
       <c r="O116" t="n">
-        <v>0.869601</v>
+        <v>0.861779</v>
       </c>
       <c r="P116" t="n">
-        <v>0.757815</v>
+        <v>0.750874</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.699271</v>
+        <v>0.692657</v>
       </c>
       <c r="R116" t="n">
-        <v>0.642343</v>
+        <v>0.635984</v>
       </c>
       <c r="S116" t="n">
-        <v>0.591428</v>
+        <v>0.585207</v>
       </c>
       <c r="T116" t="n">
-        <v>0.5423559999999999</v>
+        <v>0.5361669999999999</v>
       </c>
       <c r="U116" t="n">
-        <v>0.499334</v>
+        <v>0.492978</v>
       </c>
       <c r="V116" t="n">
-        <v>0.466703</v>
+        <v>0.459815</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6.472034</v>
+        <v>6.472899</v>
       </c>
       <c r="F117" t="n">
-        <v>8.412164000000001</v>
+        <v>8.415929999999999</v>
       </c>
       <c r="G117" t="n">
-        <v>9.627732</v>
+        <v>9.634091</v>
       </c>
       <c r="H117" t="n">
-        <v>10.199173</v>
+        <v>10.207423</v>
       </c>
       <c r="I117" t="n">
-        <v>10.318336</v>
+        <v>10.32774</v>
       </c>
       <c r="J117" t="n">
-        <v>9.24774</v>
+        <v>9.256843999999999</v>
       </c>
       <c r="K117" t="n">
-        <v>7.947312</v>
+        <v>7.95555</v>
       </c>
       <c r="L117" t="n">
-        <v>6.609671</v>
+        <v>6.616804</v>
       </c>
       <c r="M117" t="n">
-        <v>5.691583</v>
+        <v>5.697911</v>
       </c>
       <c r="N117" t="n">
-        <v>4.835123</v>
+        <v>4.840358</v>
       </c>
       <c r="O117" t="n">
-        <v>4.024282</v>
+        <v>4.028412</v>
       </c>
       <c r="P117" t="n">
-        <v>3.361577</v>
+        <v>3.364869</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.998951</v>
+        <v>3.001821</v>
       </c>
       <c r="R117" t="n">
-        <v>2.67932</v>
+        <v>2.681875</v>
       </c>
       <c r="S117" t="n">
-        <v>2.408556</v>
+        <v>2.410884</v>
       </c>
       <c r="T117" t="n">
-        <v>2.163701</v>
+        <v>2.165871</v>
       </c>
       <c r="U117" t="n">
-        <v>1.956216</v>
+        <v>1.95832</v>
       </c>
       <c r="V117" t="n">
-        <v>1.797488</v>
+        <v>1.799668</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5.599951</v>
+        <v>5.600941</v>
       </c>
       <c r="F118" t="n">
-        <v>5.773318</v>
+        <v>5.774872</v>
       </c>
       <c r="G118" t="n">
-        <v>5.833865</v>
+        <v>5.835535</v>
       </c>
       <c r="H118" t="n">
-        <v>5.748036</v>
+        <v>5.749572</v>
       </c>
       <c r="I118" t="n">
-        <v>5.591825</v>
+        <v>5.593089</v>
       </c>
       <c r="J118" t="n">
-        <v>4.916177</v>
+        <v>4.917005</v>
       </c>
       <c r="K118" t="n">
-        <v>4.192719</v>
+        <v>4.193123</v>
       </c>
       <c r="L118" t="n">
-        <v>3.483141</v>
+        <v>3.483187</v>
       </c>
       <c r="M118" t="n">
-        <v>3.017258</v>
+        <v>3.017025</v>
       </c>
       <c r="N118" t="n">
-        <v>2.593906</v>
+        <v>2.593326</v>
       </c>
       <c r="O118" t="n">
-        <v>2.19356</v>
+        <v>2.192706</v>
       </c>
       <c r="P118" t="n">
-        <v>1.865225</v>
+        <v>1.864205</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.694797</v>
+        <v>1.693627</v>
       </c>
       <c r="R118" t="n">
-        <v>1.54151</v>
+        <v>1.540219</v>
       </c>
       <c r="S118" t="n">
-        <v>1.409319</v>
+        <v>1.407906</v>
       </c>
       <c r="T118" t="n">
-        <v>1.285616</v>
+        <v>1.284074</v>
       </c>
       <c r="U118" t="n">
-        <v>1.178097</v>
+        <v>1.176394</v>
       </c>
       <c r="V118" t="n">
-        <v>1.094471</v>
+        <v>1.092519</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2.468967</v>
+        <v>2.468724</v>
       </c>
       <c r="F119" t="n">
-        <v>3.071613</v>
+        <v>3.071853</v>
       </c>
       <c r="G119" t="n">
-        <v>3.693268</v>
+        <v>3.694372</v>
       </c>
       <c r="H119" t="n">
-        <v>4.170264</v>
+        <v>4.172257</v>
       </c>
       <c r="I119" t="n">
-        <v>4.476456</v>
+        <v>4.479144</v>
       </c>
       <c r="J119" t="n">
-        <v>4.225681</v>
+        <v>4.228545</v>
       </c>
       <c r="K119" t="n">
-        <v>3.799767</v>
+        <v>3.8025</v>
       </c>
       <c r="L119" t="n">
-        <v>3.293867</v>
+        <v>3.296306</v>
       </c>
       <c r="M119" t="n">
-        <v>2.954206</v>
+        <v>2.956417</v>
       </c>
       <c r="N119" t="n">
-        <v>2.615654</v>
+        <v>2.617476</v>
       </c>
       <c r="O119" t="n">
-        <v>2.265296</v>
+        <v>2.266707</v>
       </c>
       <c r="P119" t="n">
-        <v>1.961594</v>
+        <v>1.96269</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.805814</v>
+        <v>1.806742</v>
       </c>
       <c r="R119" t="n">
-        <v>1.657184</v>
+        <v>1.657981</v>
       </c>
       <c r="S119" t="n">
-        <v>1.523307</v>
+        <v>1.523998</v>
       </c>
       <c r="T119" t="n">
-        <v>1.392723</v>
+        <v>1.393331</v>
       </c>
       <c r="U119" t="n">
-        <v>1.27516</v>
+        <v>1.275712</v>
       </c>
       <c r="V119" t="n">
-        <v>1.179881</v>
+        <v>1.180416</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.00173</v>
+        <v>0.00127</v>
       </c>
       <c r="F120" t="n">
-        <v>0.003125</v>
+        <v>0.002295</v>
       </c>
       <c r="G120" t="n">
+        <v>0.003091</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.003713</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.004211</v>
+      </c>
+      <c r="J120" t="n">
         <v>0.004208</v>
       </c>
-      <c r="H120" t="n">
-        <v>0.005054</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0.005731</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0.005727</v>
-      </c>
       <c r="K120" t="n">
-        <v>0.005455</v>
+        <v>0.00401</v>
       </c>
       <c r="L120" t="n">
-        <v>0.005015</v>
+        <v>0.003686</v>
       </c>
       <c r="M120" t="n">
-        <v>0.004765</v>
+        <v>0.003503</v>
       </c>
       <c r="N120" t="n">
-        <v>0.00441</v>
+        <v>0.003242</v>
       </c>
       <c r="O120" t="n">
-        <v>0.00396</v>
+        <v>0.002911</v>
       </c>
       <c r="P120" t="n">
-        <v>0.003565</v>
+        <v>0.002621</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.003446</v>
+        <v>0.002533</v>
       </c>
       <c r="R120" t="n">
-        <v>0.00336</v>
+        <v>0.00247</v>
       </c>
       <c r="S120" t="n">
-        <v>0.003332</v>
+        <v>0.00245</v>
       </c>
       <c r="T120" t="n">
-        <v>0.003356</v>
+        <v>0.002468</v>
       </c>
       <c r="U120" t="n">
-        <v>0.003482</v>
+        <v>0.002562</v>
       </c>
       <c r="V120" t="n">
-        <v>0.003802</v>
+        <v>0.002798</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.027242</v>
+        <v>0.019998</v>
       </c>
       <c r="F121" t="n">
-        <v>0.04345</v>
+        <v>0.031908</v>
       </c>
       <c r="G121" t="n">
-        <v>0.053175</v>
+        <v>0.03906</v>
       </c>
       <c r="H121" t="n">
-        <v>0.060327</v>
+        <v>0.044322</v>
       </c>
       <c r="I121" t="n">
-        <v>0.066556</v>
+        <v>0.048905</v>
       </c>
       <c r="J121" t="n">
-        <v>0.06590600000000001</v>
+        <v>0.048434</v>
       </c>
       <c r="K121" t="n">
-        <v>0.062904</v>
+        <v>0.046232</v>
       </c>
       <c r="L121" t="n">
-        <v>0.058251</v>
+        <v>0.042817</v>
       </c>
       <c r="M121" t="n">
-        <v>0.055842</v>
+        <v>0.04105</v>
       </c>
       <c r="N121" t="n">
-        <v>0.052613</v>
+        <v>0.038678</v>
       </c>
       <c r="O121" t="n">
-        <v>0.048159</v>
+        <v>0.035404</v>
       </c>
       <c r="P121" t="n">
-        <v>0.044049</v>
+        <v>0.032383</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.043058</v>
+        <v>0.031656</v>
       </c>
       <c r="R121" t="n">
-        <v>0.042374</v>
+        <v>0.031156</v>
       </c>
       <c r="S121" t="n">
-        <v>0.042391</v>
+        <v>0.031173</v>
       </c>
       <c r="T121" t="n">
-        <v>0.043028</v>
+        <v>0.031647</v>
       </c>
       <c r="U121" t="n">
-        <v>0.0449</v>
+        <v>0.033034</v>
       </c>
       <c r="V121" t="n">
-        <v>0.04921</v>
+        <v>0.036221</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>114.325626</v>
+        <v>114.335623</v>
       </c>
       <c r="F122" t="n">
-        <v>124.665262</v>
+        <v>124.679063</v>
       </c>
       <c r="G122" t="n">
-        <v>135.486675</v>
+        <v>135.502087</v>
       </c>
       <c r="H122" t="n">
-        <v>143.569586</v>
+        <v>143.586219</v>
       </c>
       <c r="I122" t="n">
-        <v>149.732697</v>
+        <v>149.750911</v>
       </c>
       <c r="J122" t="n">
-        <v>140.582429</v>
+        <v>140.600851</v>
       </c>
       <c r="K122" t="n">
-        <v>127.532958</v>
+        <v>127.551185</v>
       </c>
       <c r="L122" t="n">
-        <v>112.155713</v>
+        <v>112.173252</v>
       </c>
       <c r="M122" t="n">
-        <v>102.212415</v>
+        <v>102.229879</v>
       </c>
       <c r="N122" t="n">
-        <v>93.423378</v>
+        <v>93.440849</v>
       </c>
       <c r="O122" t="n">
-        <v>84.137946</v>
+        <v>84.15488499999999</v>
       </c>
       <c r="P122" t="n">
-        <v>75.646638</v>
+        <v>75.66282200000001</v>
       </c>
       <c r="Q122" t="n">
-        <v>71.956543</v>
+        <v>71.972843</v>
       </c>
       <c r="R122" t="n">
-        <v>68.104665</v>
+        <v>68.12106900000001</v>
       </c>
       <c r="S122" t="n">
-        <v>64.562105</v>
+        <v>64.57881999999999</v>
       </c>
       <c r="T122" t="n">
-        <v>60.872768</v>
+        <v>60.88999</v>
       </c>
       <c r="U122" t="n">
-        <v>57.449573</v>
+        <v>57.467761</v>
       </c>
       <c r="V122" t="n">
-        <v>54.750064</v>
+        <v>54.770182</v>
       </c>
     </row>
     <row r="123">
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.771604</v>
+        <v>0.771355</v>
       </c>
       <c r="F123" t="n">
-        <v>0.752541</v>
+        <v>0.752385</v>
       </c>
       <c r="G123" t="n">
-        <v>0.675751</v>
+        <v>0.675601</v>
       </c>
       <c r="H123" t="n">
-        <v>0.60195</v>
+        <v>0.601838</v>
       </c>
       <c r="I123" t="n">
-        <v>0.537745</v>
+        <v>0.5376840000000001</v>
       </c>
       <c r="J123" t="n">
         <v>0.466271</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6.42661</v>
+        <v>6.416518</v>
       </c>
       <c r="F124" t="n">
-        <v>5.974922</v>
+        <v>5.969369</v>
       </c>
       <c r="G124" t="n">
-        <v>5.412006</v>
+        <v>5.408246</v>
       </c>
       <c r="H124" t="n">
-        <v>4.910829</v>
+        <v>4.908485</v>
       </c>
       <c r="I124" t="n">
-        <v>4.528268</v>
+        <v>4.527163</v>
       </c>
       <c r="J124" t="n">
         <v>4.068714</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>15.809499</v>
+        <v>15.819841</v>
       </c>
       <c r="F125" t="n">
-        <v>15.983707</v>
+        <v>15.989417</v>
       </c>
       <c r="G125" t="n">
-        <v>15.977622</v>
+        <v>15.981533</v>
       </c>
       <c r="H125" t="n">
-        <v>15.411593</v>
+        <v>15.41405</v>
       </c>
       <c r="I125" t="n">
-        <v>14.55616</v>
+        <v>14.557327</v>
       </c>
       <c r="J125" t="n">
         <v>13.000744</v>
@@ -10254,58 +10254,58 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>58.59511</v>
+        <v>58.604395</v>
       </c>
       <c r="F130" t="n">
-        <v>64.300605</v>
+        <v>64.316524</v>
       </c>
       <c r="G130" t="n">
-        <v>71.837259</v>
+        <v>71.858814</v>
       </c>
       <c r="H130" t="n">
-        <v>78.939886</v>
+        <v>78.966399</v>
       </c>
       <c r="I130" t="n">
-        <v>89.57202700000001</v>
+        <v>89.604398</v>
       </c>
       <c r="J130" t="n">
-        <v>86.747665</v>
+        <v>86.780604</v>
       </c>
       <c r="K130" t="n">
-        <v>81.91440799999999</v>
+        <v>81.946529</v>
       </c>
       <c r="L130" t="n">
-        <v>76.144223</v>
+        <v>76.17487</v>
       </c>
       <c r="M130" t="n">
-        <v>72.829701</v>
+        <v>72.859678</v>
       </c>
       <c r="N130" t="n">
-        <v>68.65601599999999</v>
+        <v>68.684831</v>
       </c>
       <c r="O130" t="n">
-        <v>64.54024699999999</v>
+        <v>64.56781100000001</v>
       </c>
       <c r="P130" t="n">
-        <v>63.670828</v>
+        <v>63.698404</v>
       </c>
       <c r="Q130" t="n">
-        <v>62.487063</v>
+        <v>62.514363</v>
       </c>
       <c r="R130" t="n">
-        <v>58.228725</v>
+        <v>58.254129</v>
       </c>
       <c r="S130" t="n">
-        <v>54.398209</v>
+        <v>54.42173</v>
       </c>
       <c r="T130" t="n">
-        <v>49.79795</v>
+        <v>49.819215</v>
       </c>
       <c r="U130" t="n">
-        <v>44.921948</v>
+        <v>44.940907</v>
       </c>
       <c r="V130" t="n">
-        <v>40.189086</v>
+        <v>40.205883</v>
       </c>
     </row>
     <row r="131">
@@ -10330,58 +10330,58 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>9.494325999999999</v>
+        <v>9.495711999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>11.642412</v>
+        <v>11.645139</v>
       </c>
       <c r="G131" t="n">
-        <v>13.062153</v>
+        <v>13.065838</v>
       </c>
       <c r="H131" t="n">
-        <v>14.064906</v>
+        <v>14.069291</v>
       </c>
       <c r="I131" t="n">
-        <v>15.6768</v>
+        <v>15.681997</v>
       </c>
       <c r="J131" t="n">
-        <v>15.134606</v>
+        <v>15.139834</v>
       </c>
       <c r="K131" t="n">
-        <v>14.390565</v>
+        <v>14.395669</v>
       </c>
       <c r="L131" t="n">
-        <v>13.534555</v>
+        <v>13.539462</v>
       </c>
       <c r="M131" t="n">
-        <v>13.082255</v>
+        <v>13.087086</v>
       </c>
       <c r="N131" t="n">
-        <v>12.41366</v>
+        <v>12.418311</v>
       </c>
       <c r="O131" t="n">
-        <v>11.735657</v>
+        <v>11.740104</v>
       </c>
       <c r="P131" t="n">
-        <v>11.624034</v>
+        <v>11.628463</v>
       </c>
       <c r="Q131" t="n">
-        <v>11.410084</v>
+        <v>11.414419</v>
       </c>
       <c r="R131" t="n">
-        <v>10.560861</v>
+        <v>10.564805</v>
       </c>
       <c r="S131" t="n">
-        <v>9.737555</v>
+        <v>9.74109</v>
       </c>
       <c r="T131" t="n">
-        <v>8.764257000000001</v>
+        <v>8.767329</v>
       </c>
       <c r="U131" t="n">
-        <v>7.76955</v>
+        <v>7.772178</v>
       </c>
       <c r="V131" t="n">
-        <v>6.837117</v>
+        <v>6.839351</v>
       </c>
     </row>
     <row r="132">
@@ -10406,58 +10406,58 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>178.674785</v>
+        <v>178.679999</v>
       </c>
       <c r="F132" t="n">
-        <v>178.969531</v>
+        <v>178.972609</v>
       </c>
       <c r="G132" t="n">
-        <v>177.079754</v>
+        <v>177.075093</v>
       </c>
       <c r="H132" t="n">
-        <v>172.089725</v>
+        <v>172.076735</v>
       </c>
       <c r="I132" t="n">
-        <v>177.835878</v>
+        <v>177.816364</v>
       </c>
       <c r="J132" t="n">
-        <v>163.21129</v>
+        <v>163.191846</v>
       </c>
       <c r="K132" t="n">
-        <v>150.562073</v>
+        <v>150.545973</v>
       </c>
       <c r="L132" t="n">
-        <v>138.749657</v>
+        <v>138.737989</v>
       </c>
       <c r="M132" t="n">
-        <v>131.728672</v>
+        <v>131.720681</v>
       </c>
       <c r="N132" t="n">
-        <v>122.580908</v>
+        <v>122.575804</v>
       </c>
       <c r="O132" t="n">
-        <v>113.335526</v>
+        <v>113.33224</v>
       </c>
       <c r="P132" t="n">
-        <v>109.370393</v>
+        <v>109.367723</v>
       </c>
       <c r="Q132" t="n">
-        <v>104.22423</v>
+        <v>104.221227</v>
       </c>
       <c r="R132" t="n">
-        <v>93.882886</v>
+        <v>93.87918000000001</v>
       </c>
       <c r="S132" t="n">
-        <v>84.84683099999999</v>
+        <v>84.84240800000001</v>
       </c>
       <c r="T132" t="n">
-        <v>75.581813</v>
+        <v>75.57699700000001</v>
       </c>
       <c r="U132" t="n">
-        <v>66.98280200000001</v>
+        <v>66.97794500000001</v>
       </c>
       <c r="V132" t="n">
-        <v>59.509737</v>
+        <v>59.505132</v>
       </c>
     </row>
     <row r="133">
@@ -10482,58 +10482,58 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>39.272492</v>
+        <v>39.259766</v>
       </c>
       <c r="F133" t="n">
-        <v>58.668238</v>
+        <v>58.655614</v>
       </c>
       <c r="G133" t="n">
-        <v>83.296931</v>
+        <v>83.29090100000001</v>
       </c>
       <c r="H133" t="n">
-        <v>104.172833</v>
+        <v>104.173669</v>
       </c>
       <c r="I133" t="n">
-        <v>124.14658</v>
+        <v>124.151278</v>
       </c>
       <c r="J133" t="n">
-        <v>121.392598</v>
+        <v>121.397195</v>
       </c>
       <c r="K133" t="n">
-        <v>114.374321</v>
+        <v>114.377205</v>
       </c>
       <c r="L133" t="n">
-        <v>106.358338</v>
+        <v>106.359604</v>
       </c>
       <c r="M133" t="n">
-        <v>102.577771</v>
+        <v>102.578091</v>
       </c>
       <c r="N133" t="n">
-        <v>98.23906100000001</v>
+        <v>98.23904400000001</v>
       </c>
       <c r="O133" t="n">
-        <v>94.656014</v>
+        <v>94.65608400000001</v>
       </c>
       <c r="P133" t="n">
-        <v>96.49812799999999</v>
+        <v>96.498594</v>
       </c>
       <c r="Q133" t="n">
-        <v>98.590248</v>
+        <v>98.59156900000001</v>
       </c>
       <c r="R133" t="n">
-        <v>95.941193</v>
+        <v>95.94343000000001</v>
       </c>
       <c r="S133" t="n">
-        <v>93.62672600000001</v>
+        <v>93.62988900000001</v>
       </c>
       <c r="T133" t="n">
-        <v>89.422937</v>
+        <v>89.42683599999999</v>
       </c>
       <c r="U133" t="n">
-        <v>84.155541</v>
+        <v>84.159987</v>
       </c>
       <c r="V133" t="n">
-        <v>78.580184</v>
+        <v>78.584993</v>
       </c>
     </row>
     <row r="134">
@@ -10558,58 +10558,58 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>19.315835</v>
+        <v>19.317638</v>
       </c>
       <c r="F134" t="n">
-        <v>17.988712</v>
+        <v>17.990398</v>
       </c>
       <c r="G134" t="n">
-        <v>17.163015</v>
+        <v>17.163606</v>
       </c>
       <c r="H134" t="n">
-        <v>16.714335</v>
+        <v>16.713691</v>
       </c>
       <c r="I134" t="n">
-        <v>17.549765</v>
+        <v>17.547966</v>
       </c>
       <c r="J134" t="n">
-        <v>16.323292</v>
+        <v>16.320801</v>
       </c>
       <c r="K134" t="n">
-        <v>15.154011</v>
+        <v>15.151087</v>
       </c>
       <c r="L134" t="n">
-        <v>14.047117</v>
+        <v>14.043935</v>
       </c>
       <c r="M134" t="n">
-        <v>13.479259</v>
+        <v>13.475782</v>
       </c>
       <c r="N134" t="n">
-        <v>12.810948</v>
+        <v>12.807275</v>
       </c>
       <c r="O134" t="n">
-        <v>12.29482</v>
+        <v>12.291004</v>
       </c>
       <c r="P134" t="n">
-        <v>12.565223</v>
+        <v>12.56115</v>
       </c>
       <c r="Q134" t="n">
-        <v>12.926394</v>
+        <v>12.92215</v>
       </c>
       <c r="R134" t="n">
-        <v>12.694755</v>
+        <v>12.690592</v>
       </c>
       <c r="S134" t="n">
-        <v>12.527795</v>
+        <v>12.523718</v>
       </c>
       <c r="T134" t="n">
-        <v>12.13931</v>
+        <v>12.135405</v>
       </c>
       <c r="U134" t="n">
-        <v>11.635265</v>
+        <v>11.631579</v>
       </c>
       <c r="V134" t="n">
-        <v>11.112003</v>
+        <v>11.108552</v>
       </c>
     </row>
     <row r="135">
@@ -10634,58 +10634,58 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>7.304502</v>
+        <v>7.301586</v>
       </c>
       <c r="F135" t="n">
-        <v>9.261115</v>
+        <v>9.256598</v>
       </c>
       <c r="G135" t="n">
-        <v>11.698079</v>
+        <v>11.692793</v>
       </c>
       <c r="H135" t="n">
-        <v>13.810646</v>
+        <v>13.80499</v>
       </c>
       <c r="I135" t="n">
-        <v>16.331521</v>
+        <v>16.325234</v>
       </c>
       <c r="J135" t="n">
-        <v>16.272514</v>
+        <v>16.266382</v>
       </c>
       <c r="K135" t="n">
-        <v>15.753863</v>
+        <v>15.747936</v>
       </c>
       <c r="L135" t="n">
-        <v>15.029116</v>
+        <v>15.023436</v>
       </c>
       <c r="M135" t="n">
-        <v>14.766469</v>
+        <v>14.760892</v>
       </c>
       <c r="N135" t="n">
-        <v>14.276368</v>
+        <v>14.270984</v>
       </c>
       <c r="O135" t="n">
-        <v>13.765002</v>
+        <v>13.759819</v>
       </c>
       <c r="P135" t="n">
-        <v>13.887641</v>
+        <v>13.882372</v>
       </c>
       <c r="Q135" t="n">
-        <v>13.858121</v>
+        <v>13.852737</v>
       </c>
       <c r="R135" t="n">
-        <v>13.017052</v>
+        <v>13.01175</v>
       </c>
       <c r="S135" t="n">
-        <v>12.159441</v>
+        <v>12.15417</v>
       </c>
       <c r="T135" t="n">
-        <v>11.069382</v>
+        <v>11.064243</v>
       </c>
       <c r="U135" t="n">
-        <v>9.914080999999999</v>
+        <v>9.909162</v>
       </c>
       <c r="V135" t="n">
-        <v>8.813370000000001</v>
+        <v>8.808702</v>
       </c>
     </row>
     <row r="136">
@@ -10710,58 +10710,58 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>26.851151</v>
+        <v>26.855493</v>
       </c>
       <c r="F136" t="n">
-        <v>25.295124</v>
+        <v>25.301339</v>
       </c>
       <c r="G136" t="n">
-        <v>22.755351</v>
+        <v>22.76168</v>
       </c>
       <c r="H136" t="n">
-        <v>20.145768</v>
+        <v>20.151379</v>
       </c>
       <c r="I136" t="n">
-        <v>19.938231</v>
+        <v>19.94359</v>
       </c>
       <c r="J136" t="n">
-        <v>18.058471</v>
+        <v>18.063191</v>
       </c>
       <c r="K136" t="n">
-        <v>16.680537</v>
+        <v>16.68486</v>
       </c>
       <c r="L136" t="n">
-        <v>15.655696</v>
+        <v>15.659846</v>
       </c>
       <c r="M136" t="n">
-        <v>15.43369</v>
+        <v>15.437969</v>
       </c>
       <c r="N136" t="n">
-        <v>14.991187</v>
+        <v>14.995517</v>
       </c>
       <c r="O136" t="n">
-        <v>14.486954</v>
+        <v>14.491284</v>
       </c>
       <c r="P136" t="n">
-        <v>14.648338</v>
+        <v>14.65283</v>
       </c>
       <c r="Q136" t="n">
-        <v>14.675721</v>
+        <v>14.680292</v>
       </c>
       <c r="R136" t="n">
-        <v>13.877443</v>
+        <v>13.881763</v>
       </c>
       <c r="S136" t="n">
-        <v>13.085651</v>
+        <v>13.089674</v>
       </c>
       <c r="T136" t="n">
-        <v>12.042071</v>
+        <v>12.045705</v>
       </c>
       <c r="U136" t="n">
-        <v>10.901746</v>
+        <v>10.904976</v>
       </c>
       <c r="V136" t="n">
-        <v>9.780469999999999</v>
+        <v>9.78332</v>
       </c>
     </row>
     <row r="137">
@@ -10786,58 +10786,58 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7.63874</v>
+        <v>7.638886</v>
       </c>
       <c r="F137" t="n">
-        <v>7.889286</v>
+        <v>7.889454</v>
       </c>
       <c r="G137" t="n">
-        <v>7.729961</v>
+        <v>7.729789</v>
       </c>
       <c r="H137" t="n">
-        <v>7.481334</v>
+        <v>7.480802</v>
       </c>
       <c r="I137" t="n">
-        <v>7.697064</v>
+        <v>7.696261</v>
       </c>
       <c r="J137" t="n">
-        <v>6.971793</v>
+        <v>6.970963</v>
       </c>
       <c r="K137" t="n">
-        <v>6.272173</v>
+        <v>6.271395</v>
       </c>
       <c r="L137" t="n">
-        <v>5.606701</v>
+        <v>5.605994</v>
       </c>
       <c r="M137" t="n">
-        <v>5.163542</v>
+        <v>5.162865</v>
       </c>
       <c r="N137" t="n">
-        <v>4.674644</v>
+        <v>4.673984</v>
       </c>
       <c r="O137" t="n">
-        <v>4.246701</v>
+        <v>4.246065</v>
       </c>
       <c r="P137" t="n">
-        <v>4.087993</v>
+        <v>4.087371</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.948986</v>
+        <v>3.948398</v>
       </c>
       <c r="R137" t="n">
-        <v>3.634733</v>
+        <v>3.634206</v>
       </c>
       <c r="S137" t="n">
-        <v>3.358391</v>
+        <v>3.357916</v>
       </c>
       <c r="T137" t="n">
-        <v>3.046352</v>
+        <v>3.045931</v>
       </c>
       <c r="U137" t="n">
-        <v>2.734241</v>
+        <v>2.733875</v>
       </c>
       <c r="V137" t="n">
-        <v>2.447688</v>
+        <v>2.447372</v>
       </c>
     </row>
     <row r="138">
@@ -10862,58 +10862,58 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>22.497635</v>
+        <v>22.500948</v>
       </c>
       <c r="F138" t="n">
-        <v>22.871973</v>
+        <v>22.877105</v>
       </c>
       <c r="G138" t="n">
-        <v>23.166857</v>
+        <v>23.172883</v>
       </c>
       <c r="H138" t="n">
-        <v>22.849191</v>
+        <v>22.855468</v>
       </c>
       <c r="I138" t="n">
-        <v>23.411463</v>
+        <v>23.417935</v>
       </c>
       <c r="J138" t="n">
-        <v>20.891672</v>
+        <v>20.897326</v>
       </c>
       <c r="K138" t="n">
-        <v>18.608298</v>
+        <v>18.61317</v>
       </c>
       <c r="L138" t="n">
-        <v>16.59512</v>
+        <v>16.599327</v>
       </c>
       <c r="M138" t="n">
-        <v>15.7146</v>
+        <v>15.71859</v>
       </c>
       <c r="N138" t="n">
-        <v>14.975285</v>
+        <v>14.979192</v>
       </c>
       <c r="O138" t="n">
-        <v>14.425032</v>
+        <v>14.428952</v>
       </c>
       <c r="P138" t="n">
-        <v>14.628142</v>
+        <v>14.632265</v>
       </c>
       <c r="Q138" t="n">
-        <v>14.756535</v>
+        <v>14.76081</v>
       </c>
       <c r="R138" t="n">
-        <v>14.085881</v>
+        <v>14.090001</v>
       </c>
       <c r="S138" t="n">
-        <v>13.427971</v>
+        <v>13.431881</v>
       </c>
       <c r="T138" t="n">
-        <v>12.512782</v>
+        <v>12.516381</v>
       </c>
       <c r="U138" t="n">
-        <v>11.491587</v>
+        <v>11.494849</v>
       </c>
       <c r="V138" t="n">
-        <v>10.480574</v>
+        <v>10.483511</v>
       </c>
     </row>
     <row r="139">
@@ -10938,58 +10938,58 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>32.354675</v>
+        <v>32.359581</v>
       </c>
       <c r="F139" t="n">
-        <v>34.802138</v>
+        <v>34.810346</v>
       </c>
       <c r="G139" t="n">
-        <v>38.435684</v>
+        <v>38.446646</v>
       </c>
       <c r="H139" t="n">
-        <v>41.968895</v>
+        <v>41.982299</v>
       </c>
       <c r="I139" t="n">
-        <v>47.457905</v>
+        <v>47.474229</v>
       </c>
       <c r="J139" t="n">
-        <v>45.788762</v>
+        <v>45.805317</v>
       </c>
       <c r="K139" t="n">
-        <v>43.083002</v>
+        <v>43.099088</v>
       </c>
       <c r="L139" t="n">
-        <v>39.874716</v>
+        <v>39.889994</v>
       </c>
       <c r="M139" t="n">
-        <v>37.962942</v>
+        <v>37.977815</v>
       </c>
       <c r="N139" t="n">
-        <v>35.606239</v>
+        <v>35.620462</v>
       </c>
       <c r="O139" t="n">
-        <v>33.35527</v>
+        <v>33.368829</v>
       </c>
       <c r="P139" t="n">
-        <v>32.825651</v>
+        <v>32.839186</v>
       </c>
       <c r="Q139" t="n">
-        <v>32.145667</v>
+        <v>32.159043</v>
       </c>
       <c r="R139" t="n">
-        <v>29.88845</v>
+        <v>29.900875</v>
       </c>
       <c r="S139" t="n">
-        <v>27.881304</v>
+        <v>27.892796</v>
       </c>
       <c r="T139" t="n">
-        <v>25.52064</v>
+        <v>25.531034</v>
       </c>
       <c r="U139" t="n">
-        <v>23.061824</v>
+        <v>23.071111</v>
       </c>
       <c r="V139" t="n">
-        <v>20.705899</v>
+        <v>20.714161</v>
       </c>
     </row>
     <row r="140">
@@ -11014,58 +11014,58 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>173.429617</v>
+        <v>173.453459</v>
       </c>
       <c r="F140" t="n">
-        <v>162.854925</v>
+        <v>162.886224</v>
       </c>
       <c r="G140" t="n">
-        <v>157.843301</v>
+        <v>157.874854</v>
       </c>
       <c r="H140" t="n">
-        <v>157.531044</v>
+        <v>157.561859</v>
       </c>
       <c r="I140" t="n">
-        <v>170.327681</v>
+        <v>170.360777</v>
       </c>
       <c r="J140" t="n">
-        <v>162.679372</v>
+        <v>162.711523</v>
       </c>
       <c r="K140" t="n">
-        <v>153.716043</v>
+        <v>153.746962</v>
       </c>
       <c r="L140" t="n">
-        <v>143.057542</v>
+        <v>143.086467</v>
       </c>
       <c r="M140" t="n">
-        <v>136.059611</v>
+        <v>136.086629</v>
       </c>
       <c r="N140" t="n">
-        <v>126.736582</v>
+        <v>126.760805</v>
       </c>
       <c r="O140" t="n">
-        <v>117.992506</v>
+        <v>118.01405</v>
       </c>
       <c r="P140" t="n">
-        <v>116.164552</v>
+        <v>116.184965</v>
       </c>
       <c r="Q140" t="n">
-        <v>114.620357</v>
+        <v>114.639916</v>
       </c>
       <c r="R140" t="n">
-        <v>107.786002</v>
+        <v>107.803817</v>
       </c>
       <c r="S140" t="n">
-        <v>101.725658</v>
+        <v>101.741914</v>
       </c>
       <c r="T140" t="n">
-        <v>94.13433000000001</v>
+        <v>94.148949</v>
       </c>
       <c r="U140" t="n">
-        <v>86.00499499999999</v>
+        <v>86.018108</v>
       </c>
       <c r="V140" t="n">
-        <v>78.151349</v>
+        <v>78.163186</v>
       </c>
     </row>
     <row r="141">
@@ -11090,58 +11090,58 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>7.397665</v>
+        <v>7.383275</v>
       </c>
       <c r="F141" t="n">
-        <v>8.272195</v>
+        <v>8.247152</v>
       </c>
       <c r="G141" t="n">
-        <v>9.260377999999999</v>
+        <v>9.226542</v>
       </c>
       <c r="H141" t="n">
-        <v>10.038013</v>
+        <v>9.997612</v>
       </c>
       <c r="I141" t="n">
-        <v>11.245431</v>
+        <v>11.19788</v>
       </c>
       <c r="J141" t="n">
-        <v>10.855998</v>
+        <v>10.809253</v>
       </c>
       <c r="K141" t="n">
-        <v>10.295109</v>
+        <v>10.250776</v>
       </c>
       <c r="L141" t="n">
-        <v>9.688305</v>
+        <v>9.647029</v>
       </c>
       <c r="M141" t="n">
-        <v>9.441470000000001</v>
+        <v>9.402037999999999</v>
       </c>
       <c r="N141" t="n">
-        <v>9.116258999999999</v>
+        <v>9.079381</v>
       </c>
       <c r="O141" t="n">
-        <v>8.857923</v>
+        <v>8.823651</v>
       </c>
       <c r="P141" t="n">
-        <v>9.094271000000001</v>
+        <v>9.060942000000001</v>
       </c>
       <c r="Q141" t="n">
-        <v>9.322590999999999</v>
+        <v>9.290445999999999</v>
       </c>
       <c r="R141" t="n">
-        <v>9.21308</v>
+        <v>9.184319</v>
       </c>
       <c r="S141" t="n">
-        <v>9.149203</v>
+        <v>9.123694</v>
       </c>
       <c r="T141" t="n">
-        <v>8.819901</v>
+        <v>8.797642</v>
       </c>
       <c r="U141" t="n">
-        <v>8.241913</v>
+        <v>8.222402000000001</v>
       </c>
       <c r="V141" t="n">
-        <v>7.541075</v>
+        <v>7.523747</v>
       </c>
     </row>
     <row r="142">
@@ -11166,58 +11166,58 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4.257278</v>
+        <v>4.233071</v>
       </c>
       <c r="F142" t="n">
-        <v>7.183264</v>
+        <v>7.151015</v>
       </c>
       <c r="G142" t="n">
-        <v>12.517537</v>
+        <v>12.48682</v>
       </c>
       <c r="H142" t="n">
-        <v>18.639388</v>
+        <v>18.611773</v>
       </c>
       <c r="I142" t="n">
-        <v>25.130636</v>
+        <v>25.103075</v>
       </c>
       <c r="J142" t="n">
-        <v>26.388403</v>
+        <v>26.362199</v>
       </c>
       <c r="K142" t="n">
-        <v>25.687206</v>
+        <v>25.660958</v>
       </c>
       <c r="L142" t="n">
-        <v>24.038812</v>
+        <v>24.011947</v>
       </c>
       <c r="M142" t="n">
-        <v>23.070922</v>
+        <v>23.042788</v>
       </c>
       <c r="N142" t="n">
-        <v>21.953707</v>
+        <v>21.925276</v>
       </c>
       <c r="O142" t="n">
-        <v>21.099551</v>
+        <v>21.071308</v>
       </c>
       <c r="P142" t="n">
-        <v>21.549038</v>
+        <v>21.519966</v>
       </c>
       <c r="Q142" t="n">
-        <v>22.090848</v>
+        <v>22.061476</v>
       </c>
       <c r="R142" t="n">
-        <v>21.5655</v>
+        <v>21.537694</v>
       </c>
       <c r="S142" t="n">
-        <v>21.098682</v>
+        <v>21.072537</v>
       </c>
       <c r="T142" t="n">
-        <v>20.197478</v>
+        <v>20.173536</v>
       </c>
       <c r="U142" t="n">
-        <v>19.049844</v>
+        <v>19.028258</v>
       </c>
       <c r="V142" t="n">
-        <v>17.841249</v>
+        <v>17.82189</v>
       </c>
     </row>
     <row r="143">
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.708717</v>
+        <v>0.651945</v>
       </c>
       <c r="F146" t="n">
-        <v>0.891029</v>
+        <v>0.768738</v>
       </c>
       <c r="G146" t="n">
-        <v>1.0574</v>
+        <v>0.864343</v>
       </c>
       <c r="H146" t="n">
-        <v>1.357777</v>
+        <v>1.068338</v>
       </c>
       <c r="I146" t="n">
-        <v>1.94817</v>
+        <v>1.509221</v>
       </c>
       <c r="J146" t="n">
         <v>4.225779</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.729322</v>
+        <v>0.732637</v>
       </c>
       <c r="F147" t="n">
-        <v>0.844996</v>
+        <v>0.8489950000000001</v>
       </c>
       <c r="G147" t="n">
-        <v>0.889707</v>
+        <v>0.889665</v>
       </c>
       <c r="H147" t="n">
-        <v>0.956682</v>
+        <v>0.950202</v>
       </c>
       <c r="I147" t="n">
-        <v>1.027692</v>
+        <v>1.012714</v>
       </c>
       <c r="J147" t="n">
         <v>1.048914</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>47.501422</v>
+        <v>47.55488</v>
       </c>
       <c r="F148" t="n">
-        <v>57.964914</v>
+        <v>58.083207</v>
       </c>
       <c r="G148" t="n">
-        <v>65.19868200000001</v>
+        <v>65.39178</v>
       </c>
       <c r="H148" t="n">
-        <v>73.187659</v>
+        <v>73.48357799999999</v>
       </c>
       <c r="I148" t="n">
-        <v>78.676469</v>
+        <v>79.130397</v>
       </c>
       <c r="J148" t="n">
         <v>71.023777</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>12.026297</v>
+        <v>10.050866</v>
       </c>
       <c r="F149" t="n">
-        <v>15.825153</v>
+        <v>13.565843</v>
       </c>
       <c r="G149" t="n">
-        <v>19.308305</v>
+        <v>17.031324</v>
       </c>
       <c r="H149" t="n">
-        <v>22.364087</v>
+        <v>20.362477</v>
       </c>
       <c r="I149" t="n">
-        <v>24.927419</v>
+        <v>23.595518</v>
       </c>
       <c r="J149" t="n">
         <v>24.810966</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>13.603387</v>
+        <v>16.998726</v>
       </c>
       <c r="F150" t="n">
-        <v>11.786699</v>
+        <v>15.074218</v>
       </c>
       <c r="G150" t="n">
-        <v>11.065163</v>
+        <v>14.079543</v>
       </c>
       <c r="H150" t="n">
-        <v>10.56036</v>
+        <v>13.143147</v>
       </c>
       <c r="I150" t="n">
-        <v>9.816792</v>
+        <v>11.574824</v>
       </c>
       <c r="J150" t="n">
         <v>7.683422</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>11.639469</v>
+        <v>11.820063</v>
       </c>
       <c r="F151" t="n">
-        <v>12.537119</v>
+        <v>12.864069</v>
       </c>
       <c r="G151" t="n">
-        <v>13.247485</v>
+        <v>13.739285</v>
       </c>
       <c r="H151" t="n">
-        <v>14.009354</v>
+        <v>14.540661</v>
       </c>
       <c r="I151" t="n">
-        <v>14.823183</v>
+        <v>15.216762</v>
       </c>
       <c r="J151" t="n">
         <v>14.159483</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>15.711827</v>
+        <v>15.759041</v>
       </c>
       <c r="F152" t="n">
-        <v>16.281358</v>
+        <v>16.773892</v>
       </c>
       <c r="G152" t="n">
-        <v>17.141405</v>
+        <v>17.669185</v>
       </c>
       <c r="H152" t="n">
-        <v>18.441434</v>
+        <v>18.823246</v>
       </c>
       <c r="I152" t="n">
-        <v>19.959063</v>
+        <v>20.13863</v>
       </c>
       <c r="J152" t="n">
         <v>19.522083</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>7.702396</v>
+        <v>5.879029</v>
       </c>
       <c r="F153" t="n">
-        <v>10.853625</v>
+        <v>8.791138999999999</v>
       </c>
       <c r="G153" t="n">
-        <v>13.170033</v>
+        <v>11.204944</v>
       </c>
       <c r="H153" t="n">
-        <v>15.044332</v>
+        <v>13.378688</v>
       </c>
       <c r="I153" t="n">
-        <v>16.775816</v>
+        <v>15.669842</v>
       </c>
       <c r="J153" t="n">
         <v>16.891637</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1.430778</v>
+        <v>1.606429</v>
       </c>
       <c r="F154" t="n">
-        <v>1.33386</v>
+        <v>1.548654</v>
       </c>
       <c r="G154" t="n">
-        <v>1.281235</v>
+        <v>1.489346</v>
       </c>
       <c r="H154" t="n">
-        <v>1.263762</v>
+        <v>1.43511</v>
       </c>
       <c r="I154" t="n">
-        <v>1.259053</v>
+        <v>1.36575</v>
       </c>
       <c r="J154" t="n">
         <v>1.130388</v>
@@ -12154,58 +12154,58 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2.461015</v>
+        <v>2.461007</v>
       </c>
       <c r="F155" t="n">
-        <v>3.363012</v>
+        <v>3.362992</v>
       </c>
       <c r="G155" t="n">
-        <v>4.327112</v>
+        <v>4.327075</v>
       </c>
       <c r="H155" t="n">
-        <v>5.500911</v>
+        <v>5.500849</v>
       </c>
       <c r="I155" t="n">
-        <v>6.854338</v>
+        <v>6.854247</v>
       </c>
       <c r="J155" t="n">
-        <v>7.302592</v>
+        <v>7.302481</v>
       </c>
       <c r="K155" t="n">
-        <v>7.514715</v>
+        <v>7.514591</v>
       </c>
       <c r="L155" t="n">
-        <v>7.639706</v>
+        <v>7.639573</v>
       </c>
       <c r="M155" t="n">
-        <v>8.205245</v>
+        <v>8.205095999999999</v>
       </c>
       <c r="N155" t="n">
-        <v>8.785697000000001</v>
+        <v>8.785532</v>
       </c>
       <c r="O155" t="n">
-        <v>9.178627000000001</v>
+        <v>9.178449000000001</v>
       </c>
       <c r="P155" t="n">
-        <v>9.514117000000001</v>
+        <v>9.513926</v>
       </c>
       <c r="Q155" t="n">
-        <v>10.355506</v>
+        <v>10.355288</v>
       </c>
       <c r="R155" t="n">
-        <v>11.115954</v>
+        <v>11.115708</v>
       </c>
       <c r="S155" t="n">
-        <v>11.778723</v>
+        <v>11.778446</v>
       </c>
       <c r="T155" t="n">
-        <v>12.385859</v>
+        <v>12.38554</v>
       </c>
       <c r="U155" t="n">
-        <v>13.042716</v>
+        <v>13.042334</v>
       </c>
       <c r="V155" t="n">
-        <v>14.578967</v>
+        <v>14.578458</v>
       </c>
     </row>
     <row r="156">
@@ -12230,58 +12230,58 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>25.189278</v>
+        <v>25.189284</v>
       </c>
       <c r="F156" t="n">
-        <v>32.759563</v>
+        <v>32.759582</v>
       </c>
       <c r="G156" t="n">
-        <v>39.908071</v>
+        <v>39.908112</v>
       </c>
       <c r="H156" t="n">
-        <v>47.535307</v>
+        <v>47.535378</v>
       </c>
       <c r="I156" t="n">
-        <v>55.209506</v>
+        <v>55.209614</v>
       </c>
       <c r="J156" t="n">
-        <v>54.738969</v>
+        <v>54.739098</v>
       </c>
       <c r="K156" t="n">
-        <v>52.312348</v>
+        <v>52.312491</v>
       </c>
       <c r="L156" t="n">
-        <v>49.32941</v>
+        <v>49.329561</v>
       </c>
       <c r="M156" t="n">
-        <v>49.173659</v>
+        <v>49.173823</v>
       </c>
       <c r="N156" t="n">
-        <v>48.994967</v>
+        <v>48.995145</v>
       </c>
       <c r="O156" t="n">
-        <v>47.810043</v>
+        <v>47.810233</v>
       </c>
       <c r="P156" t="n">
-        <v>46.551518</v>
+        <v>46.55172</v>
       </c>
       <c r="Q156" t="n">
-        <v>47.831475</v>
+        <v>47.831704</v>
       </c>
       <c r="R156" t="n">
-        <v>48.96647</v>
+        <v>48.966734</v>
       </c>
       <c r="S156" t="n">
-        <v>49.829912</v>
+        <v>49.830219</v>
       </c>
       <c r="T156" t="n">
-        <v>50.488513</v>
+        <v>50.488876</v>
       </c>
       <c r="U156" t="n">
-        <v>51.291426</v>
+        <v>51.291866</v>
       </c>
       <c r="V156" t="n">
-        <v>55.373103</v>
+        <v>55.373693</v>
       </c>
     </row>
     <row r="157">
@@ -12306,58 +12306,58 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.384684</v>
+        <v>0.384685</v>
       </c>
       <c r="F157" t="n">
-        <v>0.631466</v>
+        <v>0.6314689999999999</v>
       </c>
       <c r="G157" t="n">
-        <v>0.937506</v>
+        <v>0.937512</v>
       </c>
       <c r="H157" t="n">
-        <v>1.253025</v>
+        <v>1.253035</v>
       </c>
       <c r="I157" t="n">
-        <v>1.507236</v>
+        <v>1.507251</v>
       </c>
       <c r="J157" t="n">
-        <v>1.486332</v>
+        <v>1.486349</v>
       </c>
       <c r="K157" t="n">
-        <v>1.410687</v>
+        <v>1.410706</v>
       </c>
       <c r="L157" t="n">
-        <v>1.33954</v>
+        <v>1.339558</v>
       </c>
       <c r="M157" t="n">
-        <v>1.356256</v>
+        <v>1.356277</v>
       </c>
       <c r="N157" t="n">
-        <v>1.37179</v>
+        <v>1.371812</v>
       </c>
       <c r="O157" t="n">
-        <v>1.347558</v>
+        <v>1.347581</v>
       </c>
       <c r="P157" t="n">
-        <v>1.304257</v>
+        <v>1.30428</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.317888</v>
+        <v>1.317912</v>
       </c>
       <c r="R157" t="n">
-        <v>1.29714</v>
+        <v>1.297165</v>
       </c>
       <c r="S157" t="n">
-        <v>1.25594</v>
+        <v>1.255965</v>
       </c>
       <c r="T157" t="n">
-        <v>1.212203</v>
+        <v>1.21223</v>
       </c>
       <c r="U157" t="n">
-        <v>1.185191</v>
+        <v>1.185221</v>
       </c>
       <c r="V157" t="n">
-        <v>1.243395</v>
+        <v>1.243432</v>
       </c>
     </row>
     <row r="158">
@@ -12382,58 +12382,58 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5.810973</v>
+        <v>5.81098</v>
       </c>
       <c r="F158" t="n">
-        <v>6.655398</v>
+        <v>6.655412</v>
       </c>
       <c r="G158" t="n">
-        <v>7.110787</v>
+        <v>7.110805</v>
       </c>
       <c r="H158" t="n">
-        <v>7.711181</v>
+        <v>7.711204</v>
       </c>
       <c r="I158" t="n">
-        <v>8.448613</v>
+        <v>8.448642</v>
       </c>
       <c r="J158" t="n">
-        <v>8.088950000000001</v>
+        <v>8.088981</v>
       </c>
       <c r="K158" t="n">
-        <v>7.592409</v>
+        <v>7.592441</v>
       </c>
       <c r="L158" t="n">
-        <v>7.117759</v>
+        <v>7.117792</v>
       </c>
       <c r="M158" t="n">
-        <v>7.087534</v>
+        <v>7.08757</v>
       </c>
       <c r="N158" t="n">
-        <v>7.053495</v>
+        <v>7.053534</v>
       </c>
       <c r="O158" t="n">
-        <v>6.856303</v>
+        <v>6.856344</v>
       </c>
       <c r="P158" t="n">
-        <v>6.620545</v>
+        <v>6.620587</v>
       </c>
       <c r="Q158" t="n">
-        <v>6.707743</v>
+        <v>6.707787</v>
       </c>
       <c r="R158" t="n">
-        <v>6.637207</v>
+        <v>6.637251</v>
       </c>
       <c r="S158" t="n">
-        <v>6.469535</v>
+        <v>6.469578</v>
       </c>
       <c r="T158" t="n">
-        <v>6.294237</v>
+        <v>6.294278</v>
       </c>
       <c r="U158" t="n">
-        <v>6.20326</v>
+        <v>6.203303</v>
       </c>
       <c r="V158" t="n">
-        <v>6.550882</v>
+        <v>6.550934</v>
       </c>
     </row>
     <row r="159">
@@ -12458,58 +12458,58 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.468293</v>
+        <v>0.468294</v>
       </c>
       <c r="F159" t="n">
-        <v>0.582666</v>
+        <v>0.582669</v>
       </c>
       <c r="G159" t="n">
-        <v>0.689201</v>
+        <v>0.689206</v>
       </c>
       <c r="H159" t="n">
-        <v>0.798462</v>
+        <v>0.798469</v>
       </c>
       <c r="I159" t="n">
-        <v>0.906762</v>
+        <v>0.906772</v>
       </c>
       <c r="J159" t="n">
-        <v>0.877382</v>
+        <v>0.877393</v>
       </c>
       <c r="K159" t="n">
-        <v>0.82936</v>
+        <v>0.829372</v>
       </c>
       <c r="L159" t="n">
-        <v>0.7751169999999999</v>
+        <v>0.775129</v>
       </c>
       <c r="M159" t="n">
-        <v>0.758215</v>
+        <v>0.758227</v>
       </c>
       <c r="N159" t="n">
-        <v>0.733797</v>
+        <v>0.73381</v>
       </c>
       <c r="O159" t="n">
-        <v>0.695697</v>
+        <v>0.6957100000000001</v>
       </c>
       <c r="P159" t="n">
-        <v>0.659458</v>
+        <v>0.659471</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.66627</v>
+        <v>0.666284</v>
       </c>
       <c r="R159" t="n">
-        <v>0.658762</v>
+        <v>0.658776</v>
       </c>
       <c r="S159" t="n">
-        <v>0.635931</v>
+        <v>0.635946</v>
       </c>
       <c r="T159" t="n">
-        <v>0.602975</v>
+        <v>0.60299</v>
       </c>
       <c r="U159" t="n">
-        <v>0.572469</v>
+        <v>0.572485</v>
       </c>
       <c r="V159" t="n">
-        <v>0.58074</v>
+        <v>0.5807600000000001</v>
       </c>
     </row>
     <row r="160">
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2.158789</v>
+        <v>2.158781</v>
       </c>
       <c r="F160" t="n">
-        <v>2.945744</v>
+        <v>2.945725</v>
       </c>
       <c r="G160" t="n">
-        <v>3.715866</v>
+        <v>3.715833</v>
       </c>
       <c r="H160" t="n">
-        <v>4.552582</v>
+        <v>4.552532</v>
       </c>
       <c r="I160" t="n">
-        <v>5.473451</v>
+        <v>5.47338</v>
       </c>
       <c r="J160" t="n">
-        <v>5.696529</v>
+        <v>5.69645</v>
       </c>
       <c r="K160" t="n">
-        <v>5.792639</v>
+        <v>5.792557</v>
       </c>
       <c r="L160" t="n">
-        <v>5.856738</v>
+        <v>5.856656</v>
       </c>
       <c r="M160" t="n">
-        <v>6.246593</v>
+        <v>6.246509</v>
       </c>
       <c r="N160" t="n">
-        <v>6.609286</v>
+        <v>6.6092</v>
       </c>
       <c r="O160" t="n">
-        <v>6.787398</v>
+        <v>6.787312</v>
       </c>
       <c r="P160" t="n">
-        <v>6.895976</v>
+        <v>6.895889</v>
       </c>
       <c r="Q160" t="n">
-        <v>7.321208</v>
+        <v>7.321115</v>
       </c>
       <c r="R160" t="n">
-        <v>7.548302</v>
+        <v>7.548201</v>
       </c>
       <c r="S160" t="n">
-        <v>7.617866</v>
+        <v>7.617753</v>
       </c>
       <c r="T160" t="n">
-        <v>7.627825</v>
+        <v>7.627698</v>
       </c>
       <c r="U160" t="n">
-        <v>7.705359</v>
+        <v>7.705212</v>
       </c>
       <c r="V160" t="n">
-        <v>8.324870000000001</v>
+        <v>8.324679</v>
       </c>
     </row>
     <row r="161">
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2.250785</v>
+        <v>2.337526</v>
       </c>
       <c r="F162" t="n">
-        <v>1.641989</v>
+        <v>1.743188</v>
       </c>
       <c r="G162" t="n">
-        <v>1.228172</v>
+        <v>1.325454</v>
       </c>
       <c r="H162" t="n">
-        <v>0.999607</v>
+        <v>1.101277</v>
       </c>
       <c r="I162" t="n">
-        <v>0.836064</v>
+        <v>0.963235</v>
       </c>
       <c r="J162" t="n">
         <v>0.276904</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.5329660000000001</v>
+        <v>0.532452</v>
       </c>
       <c r="F163" t="n">
-        <v>0.656589</v>
+        <v>0.659957</v>
       </c>
       <c r="G163" t="n">
-        <v>0.7943210000000001</v>
+        <v>0.810513</v>
       </c>
       <c r="H163" t="n">
-        <v>0.890679</v>
+        <v>0.923998</v>
       </c>
       <c r="I163" t="n">
-        <v>0.920973</v>
+        <v>0.979342</v>
       </c>
       <c r="J163" t="n">
         <v>0.625298</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3.884062</v>
+        <v>3.341271</v>
       </c>
       <c r="F164" t="n">
-        <v>5.540673</v>
+        <v>4.704599</v>
       </c>
       <c r="G164" t="n">
-        <v>7.123765</v>
+        <v>6.149058</v>
       </c>
       <c r="H164" t="n">
-        <v>8.790203999999999</v>
+        <v>7.64644</v>
       </c>
       <c r="I164" t="n">
-        <v>11.016868</v>
+        <v>9.523819</v>
       </c>
       <c r="J164" t="n">
         <v>16.426193</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3.12612</v>
+        <v>3.031697</v>
       </c>
       <c r="F165" t="n">
-        <v>3.898773</v>
+        <v>3.712258</v>
       </c>
       <c r="G165" t="n">
-        <v>4.458671</v>
+        <v>4.081615</v>
       </c>
       <c r="H165" t="n">
-        <v>5.249565</v>
+        <v>4.562542</v>
       </c>
       <c r="I165" t="n">
-        <v>6.847956</v>
+        <v>5.61056</v>
       </c>
       <c r="J165" t="n">
         <v>12.800003</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>12.660993</v>
+        <v>9.568275999999999</v>
       </c>
       <c r="F166" t="n">
-        <v>19.178003</v>
+        <v>13.39202</v>
       </c>
       <c r="G166" t="n">
-        <v>25.96562</v>
+        <v>17.400088</v>
       </c>
       <c r="H166" t="n">
-        <v>35.547796</v>
+        <v>23.143154</v>
       </c>
       <c r="I166" t="n">
-        <v>55.284373</v>
+        <v>36.029261</v>
       </c>
       <c r="J166" t="n">
         <v>136.990026</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>77.767189</v>
+        <v>80.509136</v>
       </c>
       <c r="F167" t="n">
-        <v>80.931141</v>
+        <v>85.457396</v>
       </c>
       <c r="G167" t="n">
-        <v>83.793498</v>
+        <v>89.986887</v>
       </c>
       <c r="H167" t="n">
-        <v>85.936857</v>
+        <v>94.69411599999999</v>
       </c>
       <c r="I167" t="n">
-        <v>81.515672</v>
+        <v>95.253091</v>
       </c>
       <c r="J167" t="n">
         <v>18.516225</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1.382805</v>
+        <v>1.43196</v>
       </c>
       <c r="F168" t="n">
-        <v>1.577232</v>
+        <v>1.668548</v>
       </c>
       <c r="G168" t="n">
-        <v>1.74288</v>
+        <v>1.879921</v>
       </c>
       <c r="H168" t="n">
-        <v>1.833514</v>
+        <v>2.03631</v>
       </c>
       <c r="I168" t="n">
-        <v>1.728956</v>
+        <v>2.051837</v>
       </c>
       <c r="J168" t="n">
         <v>0.247042</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>41.290985</v>
+        <v>39.259053</v>
       </c>
       <c r="F169" t="n">
-        <v>52.677312</v>
+        <v>48.317906</v>
       </c>
       <c r="G169" t="n">
-        <v>64.872517</v>
+        <v>57.5772</v>
       </c>
       <c r="H169" t="n">
-        <v>80.520777</v>
+        <v>69.308273</v>
       </c>
       <c r="I169" t="n">
-        <v>106.229606</v>
+        <v>88.65814899999999</v>
       </c>
       <c r="J169" t="n">
         <v>181.100232</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2.266894</v>
+        <v>2.115776</v>
       </c>
       <c r="F170" t="n">
-        <v>3.249941</v>
+        <v>3.033676</v>
       </c>
       <c r="G170" t="n">
-        <v>4.205333</v>
+        <v>3.946903</v>
       </c>
       <c r="H170" t="n">
-        <v>5.134079</v>
+        <v>4.785023</v>
       </c>
       <c r="I170" t="n">
-        <v>6.302578</v>
+        <v>5.737467</v>
       </c>
       <c r="J170" t="n">
         <v>9.048864</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>10.847352</v>
+        <v>10.810521</v>
       </c>
       <c r="F171" t="n">
-        <v>12.412333</v>
+        <v>12.308801</v>
       </c>
       <c r="G171" t="n">
-        <v>13.761626</v>
+        <v>13.576378</v>
       </c>
       <c r="H171" t="n">
-        <v>14.915151</v>
+        <v>14.614701</v>
       </c>
       <c r="I171" t="n">
-        <v>16.164114</v>
+        <v>15.650912</v>
       </c>
       <c r="J171" t="n">
         <v>17.687252</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>16.869672</v>
+        <v>17.517463</v>
       </c>
       <c r="F172" t="n">
-        <v>17.103047</v>
+        <v>18.177081</v>
       </c>
       <c r="G172" t="n">
-        <v>16.265432</v>
+        <v>17.651327</v>
       </c>
       <c r="H172" t="n">
-        <v>14.876564</v>
+        <v>16.655926</v>
       </c>
       <c r="I172" t="n">
-        <v>12.489926</v>
+        <v>15.026113</v>
       </c>
       <c r="J172" t="n">
         <v>0.874861</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.151792</v>
+        <v>0.130718</v>
       </c>
       <c r="F173" t="n">
-        <v>0.22519</v>
+        <v>0.188619</v>
       </c>
       <c r="G173" t="n">
-        <v>0.300589</v>
+        <v>0.248247</v>
       </c>
       <c r="H173" t="n">
-        <v>0.395172</v>
+        <v>0.316802</v>
       </c>
       <c r="I173" t="n">
-        <v>0.565997</v>
+        <v>0.436774</v>
       </c>
       <c r="J173" t="n">
         <v>1.180898</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>87.151228</v>
+        <v>89.611487</v>
       </c>
       <c r="F174" t="n">
-        <v>91.369876</v>
+        <v>95.283581</v>
       </c>
       <c r="G174" t="n">
-        <v>93.918993</v>
+        <v>99.002735</v>
       </c>
       <c r="H174" t="n">
-        <v>94.962039</v>
+        <v>101.767011</v>
       </c>
       <c r="I174" t="n">
-        <v>90.927955</v>
+        <v>101.142562</v>
       </c>
       <c r="J174" t="n">
         <v>41.357358</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.368979</v>
+        <v>0.298662</v>
       </c>
       <c r="F175" t="n">
-        <v>0.577897</v>
+        <v>0.481765</v>
       </c>
       <c r="G175" t="n">
-        <v>0.8044559999999999</v>
+        <v>0.702592</v>
       </c>
       <c r="H175" t="n">
-        <v>1.061921</v>
+        <v>0.954024</v>
       </c>
       <c r="I175" t="n">
-        <v>1.368366</v>
+        <v>1.248502</v>
       </c>
       <c r="J175" t="n">
         <v>1.760508</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.043929</v>
+        <v>0.044132</v>
       </c>
       <c r="F176" t="n">
-        <v>0.045925</v>
+        <v>0.04561</v>
       </c>
       <c r="G176" t="n">
-        <v>0.048606</v>
+        <v>0.047502</v>
       </c>
       <c r="H176" t="n">
-        <v>0.052268</v>
+        <v>0.050145</v>
       </c>
       <c r="I176" t="n">
-        <v>0.058247</v>
+        <v>0.054504</v>
       </c>
       <c r="J176" t="n">
         <v>0.07263699999999999</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>65.936105</v>
+        <v>65.992501</v>
       </c>
       <c r="F177" t="n">
-        <v>92.39990299999999</v>
+        <v>94.312971</v>
       </c>
       <c r="G177" t="n">
-        <v>116.871251</v>
+        <v>121.773182</v>
       </c>
       <c r="H177" t="n">
-        <v>131.367229</v>
+        <v>139.98038</v>
       </c>
       <c r="I177" t="n">
-        <v>130.628721</v>
+        <v>144.532404</v>
       </c>
       <c r="J177" t="n">
         <v>65.487419</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.056304</v>
+        <v>0.054342</v>
       </c>
       <c r="F178" t="n">
-        <v>0.073569</v>
+        <v>0.069757</v>
       </c>
       <c r="G178" t="n">
-        <v>0.090585</v>
+        <v>0.08438</v>
       </c>
       <c r="H178" t="n">
-        <v>0.110152</v>
+        <v>0.100122</v>
       </c>
       <c r="I178" t="n">
-        <v>0.140304</v>
+        <v>0.122901</v>
       </c>
       <c r="J178" t="n">
         <v>0.226373</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.105813</v>
+        <v>0.106999</v>
       </c>
       <c r="F179" t="n">
-        <v>0.115979</v>
+        <v>0.117638</v>
       </c>
       <c r="G179" t="n">
-        <v>0.126039</v>
+        <v>0.128369</v>
       </c>
       <c r="H179" t="n">
-        <v>0.13292</v>
+        <v>0.136247</v>
       </c>
       <c r="I179" t="n">
-        <v>0.135228</v>
+        <v>0.140472</v>
       </c>
       <c r="J179" t="n">
         <v>0.102938</v>
@@ -14130,58 +14130,58 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>-0</v>
+        <v>-2e-06</v>
       </c>
       <c r="F181" t="n">
-        <v>4e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="G181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-9e-06</v>
+      </c>
+      <c r="J181" t="n">
         <v>-1e-06</v>
       </c>
-      <c r="H181" t="n">
+      <c r="K181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="L181" t="n">
         <v>2e-06</v>
       </c>
-      <c r="I181" t="n">
-        <v>5e-06</v>
-      </c>
-      <c r="J181" t="n">
+      <c r="M181" t="n">
         <v>0</v>
       </c>
-      <c r="K181" t="n">
-        <v>-4e-06</v>
-      </c>
-      <c r="L181" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>-3e-06</v>
-      </c>
       <c r="N181" t="n">
-        <v>-0</v>
+        <v>-5e-06</v>
       </c>
       <c r="O181" t="n">
         <v>-0</v>
       </c>
       <c r="P181" t="n">
-        <v>6e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="Q181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="R181" t="n">
         <v>2e-06</v>
       </c>
-      <c r="R181" t="n">
-        <v>1e-06</v>
-      </c>
       <c r="S181" t="n">
+        <v>-5e-06</v>
+      </c>
+      <c r="T181" t="n">
+        <v>-4e-06</v>
+      </c>
+      <c r="U181" t="n">
         <v>-2e-06</v>
       </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
+      <c r="V181" t="n">
         <v>-4e-06</v>
-      </c>
-      <c r="V181" t="n">
-        <v>-8e-06</v>
       </c>
     </row>
   </sheetData>
